--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -5,18 +5,20 @@
   <sheets>
     <sheet state="visible" name="Volunteers_table" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Volunteers_table!$M$1:$T$11</definedName>
+  </definedNames>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="lshNdn0cT7QzJf/EqCqqQdUd890t6PIUo77jFJ/SvMM="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="bggBHTTv/dWex2GdCaFNGIWy41far31VSSqBiicGAZg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="26">
   <si>
     <t>Game</t>
   </si>
@@ -48,73 +50,52 @@
     <t>Kid</t>
   </si>
   <si>
-    <t>Volunteer count</t>
+    <t>Overall</t>
   </si>
   <si>
-    <t>20/6</t>
+    <t>Tournament</t>
+  </si>
+  <si>
+    <t>Remco</t>
+  </si>
+  <si>
+    <t>Micah</t>
+  </si>
+  <si>
+    <t>Yarden</t>
+  </si>
+  <si>
+    <t>Adam</t>
+  </si>
+  <si>
+    <t>Away</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Amit A</t>
   </si>
   <si>
     <t>Home</t>
   </si>
   <si>
-    <t>Remco</t>
-  </si>
-  <si>
-    <t>Yarden</t>
+    <t>Ari</t>
   </si>
   <si>
     <t>Maddox</t>
   </si>
   <si>
-    <t>Adam</t>
+    <t>Mulu</t>
   </si>
   <si>
-    <t>Ari</t>
-  </si>
-  <si>
-    <t>Away</t>
+    <t>Amit M</t>
   </si>
   <si>
     <t>Hugo</t>
   </si>
   <si>
-    <t>Amit A</t>
-  </si>
-  <si>
-    <t>Amit M</t>
-  </si>
-  <si>
     <t>Robert</t>
-  </si>
-  <si>
-    <t>Mulu</t>
-  </si>
-  <si>
-    <t>20/7</t>
-  </si>
-  <si>
-    <t>20/8</t>
-  </si>
-  <si>
-    <t>20/9</t>
-  </si>
-  <si>
-    <t>20/10</t>
-  </si>
-  <si>
-    <t>20/11</t>
-  </si>
-  <si>
-    <t>20/12</t>
-  </si>
-  <si>
-    <t>20/13</t>
-  </si>
-  <si>
-    <t>20/14</t>
-  </si>
-  <si>
-    <t>20/15</t>
   </si>
 </sst>
 </file>
@@ -124,7 +105,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -145,11 +126,20 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF1F1F1F"/>
+      <name val="&quot;Google Sans Text&quot;"/>
     </font>
   </fonts>
   <fills count="4">
@@ -192,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -209,23 +199,30 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -457,6 +454,8 @@
     <col customWidth="1" min="3" max="3" width="18.0"/>
     <col customWidth="1" min="4" max="6" width="12.63"/>
     <col customWidth="1" min="7" max="7" width="12.5"/>
+    <col customWidth="1" min="10" max="10" width="5.13"/>
+    <col customWidth="1" min="11" max="11" width="3.5"/>
     <col customWidth="1" min="13" max="13" width="15.63"/>
   </cols>
   <sheetData>
@@ -491,1332 +490,2025 @@
       <c r="M1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="T1" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="6">
+      <c r="A2" s="7">
         <v>1.0</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="8">
+        <v>46256.0</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="M2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="7"/>
-      <c r="M2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="N2" s="9">
-        <f t="shared" ref="N2:N10" si="1">COUNTIF($D$2:$I$1000,$M2)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="10">
-        <v>46119.0</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="N3" s="9">
+      <c r="N2" s="6">
+        <f t="shared" ref="N2:S2" si="1">COUNTIF(D$2:D$963,$M2)</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="6">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="6">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="10">
-        <v>46333.0</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="M4" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="N4" s="9">
+        <v>3</v>
+      </c>
+      <c r="P2" s="6">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="M5" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q2" s="6">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="10">
-        <v>46545.0</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="M6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="N6" s="9">
+        <v>4</v>
+      </c>
+      <c r="R2" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="S2" s="6">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
+      <c r="T2" s="12">
+        <f t="shared" ref="T2:T11" si="3">SUM(N2:S2)</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="8">
+        <v>46271.0</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N3" s="6">
+        <f t="shared" ref="N3:S3" si="2">COUNTIF(D$2:D$963,$M3)</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="6">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="P3" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q3" s="6">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="R3" s="6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="S3" s="6">
+        <f t="shared" si="2"/>
+        <v>2</v>
+      </c>
+      <c r="T3" s="12">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="8">
+        <v>46278.0</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="6">
+        <f t="shared" ref="N4:S4" si="4">COUNTIF(D$2:D$963,$M4)</f>
+        <v>0</v>
+      </c>
+      <c r="O4" s="6">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="P4" s="6">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q4" s="6">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="R4" s="6">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="S4" s="6">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="T4" s="12">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="8">
+        <v>46285.0</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="6">
+        <f t="shared" ref="N5:S5" si="5">COUNTIF(D$2:D$963,$M5)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="6">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="P5" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="Q5" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="R5" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="S5" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="T5" s="12">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="7">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="8">
+        <v>46292.0</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="N6" s="6">
+        <f t="shared" ref="N6:S6" si="6">COUNTIF(D$2:D$963,$M6)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="6">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="P6" s="6">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="Q6" s="6">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="R6" s="6">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="S6" s="6">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="T6" s="12">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="7">
         <v>6.0</v>
       </c>
-      <c r="B7" s="10">
-        <v>46759.0</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="B7" s="8">
+        <v>46299.0</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="N7" s="6">
+        <f t="shared" ref="N7:S7" si="7">COUNTIF(D$2:D$963,$M7)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="P7" s="6">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="Q7" s="6">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="R7" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="S7" s="6">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T7" s="12">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="7">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="8">
+        <v>46306.0</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="M7" s="9" t="s">
+      <c r="N8" s="6">
+        <f t="shared" ref="N8:S8" si="8">COUNTIF(D$2:D$963,$M8)</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="6">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="P8" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="6">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="R8" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="S8" s="6">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T8" s="12">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="7">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="8">
+        <v>46313.0</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="N7" s="9">
-        <f t="shared" si="1"/>
+      <c r="F9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="N9" s="6">
+        <f t="shared" ref="N9:S9" si="9">COUNTIF(D$2:D$963,$M9)</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="R9" s="6">
+        <f t="shared" si="9"/>
+        <v>11</v>
+      </c>
+      <c r="S9" s="6">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T9" s="12">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="7">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="8">
+        <v>46320.0</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N10" s="6">
+        <f t="shared" ref="N10:S10" si="10">COUNTIF(D$2:D$963,$M10)</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="6">
+        <f t="shared" si="10"/>
+        <v>5</v>
+      </c>
+      <c r="P10" s="6">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="Q10" s="6">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="R10" s="6">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="S10" s="6">
+        <f t="shared" si="10"/>
+        <v>2</v>
+      </c>
+      <c r="T10" s="12">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="7">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="8">
+        <v>46327.0</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="N11" s="6">
+        <f t="shared" ref="N11:S11" si="11">COUNTIF(D$2:D$963,$M11)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="6">
+        <f t="shared" si="11"/>
+        <v>6</v>
+      </c>
+      <c r="P11" s="6">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="Q11" s="6">
+        <f t="shared" si="11"/>
         <v>1</v>
       </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="6">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="R11" s="6">
+        <f t="shared" si="11"/>
+        <v>2</v>
+      </c>
+      <c r="S11" s="6">
+        <f t="shared" si="11"/>
+        <v>5</v>
+      </c>
+      <c r="T11" s="12">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="7">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="8">
+        <v>46334.0</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
+      <c r="A13" s="7">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="8">
+        <v>46341.0</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
+      <c r="A14" s="7">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="8">
+        <v>46348.0</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
+      <c r="A15" s="7">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="8">
+        <v>46355.0</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
+      <c r="A16" s="7">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="8">
+        <v>46362.0</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H16" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="M8" s="9" t="s">
+      <c r="I16" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
+      <c r="A17" s="7">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="8">
+        <v>46369.0</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
+      <c r="A18" s="7">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="8">
+        <v>46376.0</v>
+      </c>
+      <c r="C18" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="N8" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="6">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="10">
-        <v>46972.0</v>
-      </c>
-      <c r="C9" s="11" t="s">
+      <c r="D18" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
+      <c r="A19" s="7">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="8">
+        <v>46383.0</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="M9" s="9" t="s">
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="7">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="8">
+        <v>46390.0</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="7">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="8">
+        <v>46397.0</v>
+      </c>
+      <c r="C21" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="N9" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="6">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="10">
-        <v>47184.0</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="8"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="M10" s="9" t="s">
+      <c r="D21" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="7">
+        <v>21.0</v>
+      </c>
+      <c r="B22" s="8">
+        <v>46404.0</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="9">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="6">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="6">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="10">
-        <v>47398.0</v>
-      </c>
-      <c r="C12" s="11" t="s">
+      <c r="G22" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="7">
+        <v>22.0</v>
+      </c>
+      <c r="B23" s="8">
+        <v>46411.0</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="7">
+        <v>23.0</v>
+      </c>
+      <c r="B24" s="8">
+        <v>46418.0</v>
+      </c>
+      <c r="C24" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="7">
+        <v>24.0</v>
+      </c>
+      <c r="B25" s="8">
+        <v>46425.0</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="7">
+        <v>25.0</v>
+      </c>
+      <c r="B26" s="8">
+        <v>46432.0</v>
+      </c>
+      <c r="C26" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="7">
+        <v>26.0</v>
+      </c>
+      <c r="B27" s="8">
+        <v>46439.0</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="7">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="8">
+        <v>46446.0</v>
+      </c>
+      <c r="C28" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="6">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="10">
-        <v>47610.0</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="6">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="10">
-        <v>47824.0</v>
-      </c>
-      <c r="C15" s="11" t="s">
+      <c r="F28" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="7">
+        <v>28.0</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46453.0</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H29" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="7">
+        <v>29.0</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46460.0</v>
+      </c>
+      <c r="C30" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="7">
+        <v>30.0</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46467.0</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="7">
+        <v>31.0</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46474.0</v>
+      </c>
+      <c r="C32" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="7">
+        <v>32.0</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46481.0</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="7">
+        <v>33.0</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46488.0</v>
+      </c>
+      <c r="C34" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="I34" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="7">
+        <v>34.0</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46495.0</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="7">
+        <v>35.0</v>
+      </c>
+      <c r="B36" s="8">
+        <v>46502.0</v>
+      </c>
+      <c r="C36" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="I36" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="7">
+        <v>36.0</v>
+      </c>
+      <c r="B37" s="8">
+        <v>46509.0</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="6">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="10">
-        <v>48036.0</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E16" s="8"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="6">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="8"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="6">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="10">
-        <v>48251.0</v>
-      </c>
-      <c r="C18" s="11" t="s">
+      <c r="F37" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="7">
+        <v>37.0</v>
+      </c>
+      <c r="B38" s="8">
+        <v>46516.0</v>
+      </c>
+      <c r="C38" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="7">
+        <v>38.0</v>
+      </c>
+      <c r="B39" s="8">
+        <v>46523.0</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I39" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="6">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="10">
-        <v>48464.0</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="6">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="10">
-        <v>48676.0</v>
-      </c>
-      <c r="C21" s="11" t="s">
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="7">
+        <v>39.0</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46530.0</v>
+      </c>
+      <c r="C40" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G40" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="6">
-        <v>21.0</v>
-      </c>
-      <c r="B22" s="10">
-        <v>48890.0</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="6">
-        <v>22.0</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="8"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="6">
-        <v>23.0</v>
-      </c>
-      <c r="B24" s="10">
-        <v>49102.0</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E24" s="8"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="6">
-        <v>24.0</v>
-      </c>
-      <c r="B25" s="10">
-        <v>49316.0</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="8"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="6">
-        <v>25.0</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E26" s="8"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="6">
-        <v>26.0</v>
-      </c>
-      <c r="B27" s="10">
-        <v>49528.0</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E27" s="8"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="6">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="10">
-        <v>49741.0</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="8"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="6">
-        <v>28.0</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E29" s="8"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="6">
-        <v>29.0</v>
-      </c>
-      <c r="B30" s="10">
-        <v>49955.0</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="8"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="7"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="12"/>
-      <c r="B32" s="12"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="12"/>
-      <c r="B33" s="12"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" s="12"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="12"/>
-      <c r="B35" s="12"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="12"/>
-      <c r="B36" s="12"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="12"/>
-      <c r="B37" s="12"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="12"/>
-      <c r="B38" s="12"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="12"/>
-      <c r="B39" s="12"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="12"/>
-      <c r="B40" s="12"/>
+      <c r="H40" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="11" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="12"/>
-      <c r="B41" s="12"/>
+      <c r="A41" s="7">
+        <v>40.0</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46537.0</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="12"/>
-      <c r="B42" s="12"/>
+      <c r="A42" s="15"/>
+      <c r="B42" s="15"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="12"/>
-      <c r="B43" s="12"/>
+      <c r="A43" s="15"/>
+      <c r="B43" s="15"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="12"/>
-      <c r="B44" s="12"/>
+      <c r="A44" s="15"/>
+      <c r="B44" s="15"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="12"/>
-      <c r="B45" s="12"/>
+      <c r="A45" s="15"/>
+      <c r="B45" s="15"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="12"/>
-      <c r="B46" s="12"/>
+      <c r="A46" s="15"/>
+      <c r="B46" s="15"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="12"/>
-      <c r="B47" s="12"/>
+      <c r="A47" s="15"/>
+      <c r="B47" s="15"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="12"/>
-      <c r="B48" s="12"/>
+      <c r="A48" s="15"/>
+      <c r="B48" s="15"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="12"/>
-      <c r="B49" s="12"/>
+      <c r="A49" s="15"/>
+      <c r="B49" s="15"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="12"/>
-      <c r="B50" s="12"/>
+      <c r="A50" s="15"/>
+      <c r="B50" s="15"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="12"/>
-      <c r="B51" s="12"/>
+      <c r="A51" s="15"/>
+      <c r="B51" s="15"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="12"/>
-      <c r="B52" s="12"/>
+      <c r="A52" s="15"/>
+      <c r="B52" s="15"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="12"/>
-      <c r="B53" s="12"/>
+      <c r="A53" s="15"/>
+      <c r="B53" s="15"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="12"/>
-      <c r="B54" s="12"/>
+      <c r="A54" s="15"/>
+      <c r="B54" s="15"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="12"/>
-      <c r="B55" s="12"/>
+      <c r="A55" s="15"/>
+      <c r="B55" s="15"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="12"/>
-      <c r="B56" s="12"/>
+      <c r="A56" s="15"/>
+      <c r="B56" s="15"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="12"/>
-      <c r="B57" s="12"/>
+      <c r="A57" s="15"/>
+      <c r="B57" s="15"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="12"/>
-      <c r="B58" s="12"/>
+      <c r="A58" s="15"/>
+      <c r="B58" s="15"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="12"/>
-      <c r="B59" s="12"/>
+      <c r="A59" s="15"/>
+      <c r="B59" s="15"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="12"/>
-      <c r="B60" s="12"/>
+      <c r="A60" s="15"/>
+      <c r="B60" s="15"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="12"/>
-      <c r="B61" s="12"/>
+      <c r="A61" s="15"/>
+      <c r="B61" s="15"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="12"/>
-      <c r="B62" s="12"/>
+      <c r="A62" s="15"/>
+      <c r="B62" s="15"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="12"/>
-      <c r="B63" s="12"/>
+      <c r="A63" s="15"/>
+      <c r="B63" s="15"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="12"/>
-      <c r="B64" s="12"/>
+      <c r="A64" s="15"/>
+      <c r="B64" s="15"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="12"/>
-      <c r="B65" s="12"/>
+      <c r="A65" s="15"/>
+      <c r="B65" s="15"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="12"/>
-      <c r="B66" s="12"/>
+      <c r="A66" s="15"/>
+      <c r="B66" s="15"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="12"/>
-      <c r="B67" s="12"/>
+      <c r="A67" s="15"/>
+      <c r="B67" s="15"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="12"/>
-      <c r="B68" s="12"/>
+      <c r="A68" s="15"/>
+      <c r="B68" s="15"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="12"/>
-      <c r="B69" s="12"/>
+      <c r="A69" s="15"/>
+      <c r="B69" s="15"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="12"/>
-      <c r="B70" s="12"/>
+      <c r="A70" s="15"/>
+      <c r="B70" s="15"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="12"/>
-      <c r="B71" s="12"/>
+      <c r="A71" s="15"/>
+      <c r="B71" s="15"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="12"/>
-      <c r="B72" s="12"/>
+      <c r="A72" s="15"/>
+      <c r="B72" s="15"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="12"/>
-      <c r="B73" s="12"/>
+      <c r="A73" s="15"/>
+      <c r="B73" s="15"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="12"/>
-      <c r="B74" s="12"/>
+      <c r="A74" s="15"/>
+      <c r="B74" s="15"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="12"/>
-      <c r="B75" s="12"/>
+      <c r="A75" s="15"/>
+      <c r="B75" s="15"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="12"/>
-      <c r="B76" s="12"/>
+      <c r="A76" s="15"/>
+      <c r="B76" s="15"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="12"/>
-      <c r="B77" s="12"/>
+      <c r="A77" s="15"/>
+      <c r="B77" s="15"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12"/>
+      <c r="A78" s="15"/>
+      <c r="B78" s="15"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="12"/>
-      <c r="B79" s="12"/>
+      <c r="A79" s="15"/>
+      <c r="B79" s="15"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="12"/>
-      <c r="B80" s="12"/>
+      <c r="A80" s="15"/>
+      <c r="B80" s="15"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="12"/>
-      <c r="B81" s="12"/>
+      <c r="A81" s="15"/>
+      <c r="B81" s="15"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="12"/>
-      <c r="B82" s="12"/>
+      <c r="A82" s="15"/>
+      <c r="B82" s="15"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="12"/>
-      <c r="B83" s="12"/>
+      <c r="A83" s="15"/>
+      <c r="B83" s="15"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="12"/>
-      <c r="B84" s="12"/>
+      <c r="A84" s="15"/>
+      <c r="B84" s="15"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="12"/>
-      <c r="B85" s="12"/>
+      <c r="A85" s="15"/>
+      <c r="B85" s="15"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="12"/>
-      <c r="B86" s="12"/>
+      <c r="A86" s="15"/>
+      <c r="B86" s="15"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="12"/>
-      <c r="B87" s="12"/>
+      <c r="A87" s="15"/>
+      <c r="B87" s="15"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="12"/>
-      <c r="B88" s="12"/>
+      <c r="A88" s="15"/>
+      <c r="B88" s="15"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="12"/>
-      <c r="B89" s="12"/>
+      <c r="A89" s="15"/>
+      <c r="B89" s="15"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="12"/>
-      <c r="B90" s="12"/>
+      <c r="A90" s="15"/>
+      <c r="B90" s="15"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="12"/>
-      <c r="B91" s="12"/>
+      <c r="A91" s="15"/>
+      <c r="B91" s="15"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="12"/>
-      <c r="B92" s="12"/>
+      <c r="A92" s="15"/>
+      <c r="B92" s="15"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="12"/>
-      <c r="B93" s="12"/>
+      <c r="A93" s="15"/>
+      <c r="B93" s="15"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="12"/>
-      <c r="B94" s="12"/>
+      <c r="A94" s="15"/>
+      <c r="B94" s="15"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="12"/>
-      <c r="B95" s="12"/>
+      <c r="A95" s="15"/>
+      <c r="B95" s="15"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="12"/>
-      <c r="B96" s="12"/>
+      <c r="A96" s="15"/>
+      <c r="B96" s="15"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="12"/>
-      <c r="B97" s="12"/>
+      <c r="A97" s="15"/>
+      <c r="B97" s="15"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="12"/>
-      <c r="B98" s="12"/>
+      <c r="A98" s="15"/>
+      <c r="B98" s="15"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="12"/>
-      <c r="B99" s="12"/>
+      <c r="A99" s="15"/>
+      <c r="B99" s="15"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="12"/>
-      <c r="B100" s="12"/>
+      <c r="A100" s="15"/>
+      <c r="B100" s="15"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="12"/>
-      <c r="B101" s="12"/>
+      <c r="A101" s="15"/>
+      <c r="B101" s="15"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="12"/>
-      <c r="B102" s="12"/>
+      <c r="A102" s="15"/>
+      <c r="B102" s="15"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="12"/>
-      <c r="B103" s="12"/>
+      <c r="A103" s="15"/>
+      <c r="B103" s="15"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="12"/>
-      <c r="B104" s="12"/>
+      <c r="A104" s="15"/>
+      <c r="B104" s="15"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="12"/>
-      <c r="B105" s="12"/>
+      <c r="A105" s="15"/>
+      <c r="B105" s="15"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="12"/>
-      <c r="B106" s="12"/>
+      <c r="A106" s="15"/>
+      <c r="B106" s="15"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="12"/>
-      <c r="B107" s="12"/>
+      <c r="A107" s="15"/>
+      <c r="B107" s="15"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="12"/>
-      <c r="B108" s="12"/>
+      <c r="A108" s="15"/>
+      <c r="B108" s="15"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="12"/>
-      <c r="B109" s="12"/>
+      <c r="A109" s="15"/>
+      <c r="B109" s="15"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="12"/>
-      <c r="B110" s="12"/>
+      <c r="A110" s="15"/>
+      <c r="B110" s="15"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="12"/>
-      <c r="B111" s="12"/>
+      <c r="A111" s="15"/>
+      <c r="B111" s="15"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="12"/>
-      <c r="B112" s="12"/>
+      <c r="A112" s="15"/>
+      <c r="B112" s="15"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="12"/>
-      <c r="B113" s="12"/>
+      <c r="A113" s="15"/>
+      <c r="B113" s="15"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="12"/>
-      <c r="B114" s="12"/>
+      <c r="A114" s="15"/>
+      <c r="B114" s="15"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="12"/>
-      <c r="B115" s="12"/>
+      <c r="A115" s="15"/>
+      <c r="B115" s="15"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="12"/>
-      <c r="B116" s="12"/>
+      <c r="A116" s="15"/>
+      <c r="B116" s="15"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="12"/>
-      <c r="B117" s="12"/>
+      <c r="A117" s="15"/>
+      <c r="B117" s="15"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="12"/>
-      <c r="B118" s="12"/>
+      <c r="A118" s="15"/>
+      <c r="B118" s="15"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="12"/>
-      <c r="B119" s="12"/>
+      <c r="A119" s="15"/>
+      <c r="B119" s="15"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="12"/>
-      <c r="B120" s="12"/>
+      <c r="A120" s="15"/>
+      <c r="B120" s="15"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="12"/>
-      <c r="B121" s="12"/>
+      <c r="A121" s="15"/>
+      <c r="B121" s="15"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="12"/>
-      <c r="B122" s="12"/>
+      <c r="A122" s="15"/>
+      <c r="B122" s="15"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="12"/>
-      <c r="B123" s="12"/>
+      <c r="A123" s="15"/>
+      <c r="B123" s="15"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="12"/>
-      <c r="B124" s="12"/>
+      <c r="A124" s="15"/>
+      <c r="B124" s="15"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="12"/>
-      <c r="B125" s="12"/>
+      <c r="A125" s="15"/>
+      <c r="B125" s="15"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="12"/>
-      <c r="B126" s="12"/>
+      <c r="A126" s="15"/>
+      <c r="B126" s="15"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="12"/>
-      <c r="B127" s="12"/>
+      <c r="A127" s="15"/>
+      <c r="B127" s="15"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="12"/>
-      <c r="B128" s="12"/>
+      <c r="A128" s="15"/>
+      <c r="B128" s="15"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="12"/>
-      <c r="B129" s="12"/>
+      <c r="A129" s="15"/>
+      <c r="B129" s="15"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="12"/>
-      <c r="B130" s="12"/>
+      <c r="A130" s="15"/>
+      <c r="B130" s="15"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="12"/>
-      <c r="B131" s="12"/>
+      <c r="A131" s="15"/>
+      <c r="B131" s="15"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="12"/>
-      <c r="B132" s="12"/>
+      <c r="A132" s="15"/>
+      <c r="B132" s="15"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="12"/>
-      <c r="B133" s="12"/>
+      <c r="A133" s="15"/>
+      <c r="B133" s="15"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="12"/>
-      <c r="B134" s="12"/>
+      <c r="A134" s="15"/>
+      <c r="B134" s="15"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="12"/>
-      <c r="B135" s="12"/>
+      <c r="A135" s="15"/>
+      <c r="B135" s="15"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="12"/>
-      <c r="B136" s="12"/>
+      <c r="A136" s="15"/>
+      <c r="B136" s="15"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="12"/>
-      <c r="B137" s="12"/>
+      <c r="A137" s="15"/>
+      <c r="B137" s="15"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="12"/>
-      <c r="B138" s="12"/>
+      <c r="A138" s="15"/>
+      <c r="B138" s="15"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="12"/>
-      <c r="B139" s="12"/>
+      <c r="A139" s="15"/>
+      <c r="B139" s="15"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="12"/>
-      <c r="B140" s="12"/>
+      <c r="A140" s="15"/>
+      <c r="B140" s="15"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="12"/>
-      <c r="B141" s="12"/>
+      <c r="A141" s="15"/>
+      <c r="B141" s="15"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="12"/>
-      <c r="B142" s="12"/>
+      <c r="A142" s="15"/>
+      <c r="B142" s="15"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="12"/>
-      <c r="B143" s="12"/>
+      <c r="A143" s="15"/>
+      <c r="B143" s="15"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="12"/>
-      <c r="B144" s="12"/>
+      <c r="A144" s="15"/>
+      <c r="B144" s="15"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="12"/>
-      <c r="B145" s="12"/>
+      <c r="A145" s="15"/>
+      <c r="B145" s="15"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="12"/>
-      <c r="B146" s="12"/>
+      <c r="A146" s="15"/>
+      <c r="B146" s="15"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="12"/>
-      <c r="B147" s="12"/>
+      <c r="A147" s="15"/>
+      <c r="B147" s="15"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="12"/>
-      <c r="B148" s="12"/>
+      <c r="A148" s="15"/>
+      <c r="B148" s="15"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="12"/>
-      <c r="B149" s="12"/>
+      <c r="A149" s="15"/>
+      <c r="B149" s="15"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="12"/>
-      <c r="B150" s="12"/>
+      <c r="A150" s="15"/>
+      <c r="B150" s="15"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="12"/>
-      <c r="B151" s="12"/>
+      <c r="A151" s="15"/>
+      <c r="B151" s="15"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="12"/>
-      <c r="B152" s="12"/>
+      <c r="A152" s="15"/>
+      <c r="B152" s="15"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="12"/>
-      <c r="B153" s="12"/>
+      <c r="A153" s="15"/>
+      <c r="B153" s="15"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="12"/>
-      <c r="B154" s="12"/>
+      <c r="A154" s="15"/>
+      <c r="B154" s="15"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="12"/>
-      <c r="B155" s="12"/>
+      <c r="A155" s="15"/>
+      <c r="B155" s="15"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="12"/>
-      <c r="B156" s="12"/>
+      <c r="A156" s="15"/>
+      <c r="B156" s="15"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="12"/>
-      <c r="B157" s="12"/>
+      <c r="A157" s="15"/>
+      <c r="B157" s="15"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="12"/>
-      <c r="B158" s="12"/>
+      <c r="A158" s="15"/>
+      <c r="B158" s="15"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="12"/>
-      <c r="B159" s="12"/>
+      <c r="A159" s="15"/>
+      <c r="B159" s="15"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="12"/>
-      <c r="B160" s="12"/>
+      <c r="A160" s="15"/>
+      <c r="B160" s="15"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="12"/>
-      <c r="B161" s="12"/>
+      <c r="A161" s="15"/>
+      <c r="B161" s="15"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="12"/>
-      <c r="B162" s="12"/>
+      <c r="A162" s="15"/>
+      <c r="B162" s="15"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="12"/>
-      <c r="B163" s="12"/>
+      <c r="A163" s="15"/>
+      <c r="B163" s="15"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="12"/>
-      <c r="B164" s="12"/>
+      <c r="A164" s="15"/>
+      <c r="B164" s="15"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="12"/>
-      <c r="B165" s="12"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="12"/>
-      <c r="B166" s="12"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="12"/>
-      <c r="B167" s="12"/>
-    </row>
-    <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="12"/>
-      <c r="B168" s="12"/>
-    </row>
-    <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="12"/>
-      <c r="B169" s="12"/>
-    </row>
-    <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="12"/>
-      <c r="B170" s="12"/>
-    </row>
-    <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="12"/>
-      <c r="B171" s="12"/>
-    </row>
-    <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="12"/>
-      <c r="B172" s="12"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="12"/>
-      <c r="B173" s="12"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="12"/>
-      <c r="B174" s="12"/>
-    </row>
-    <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="12"/>
-      <c r="B175" s="12"/>
-    </row>
-    <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="12"/>
-      <c r="B176" s="12"/>
-    </row>
-    <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="12"/>
-      <c r="B177" s="12"/>
-    </row>
-    <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="12"/>
-      <c r="B178" s="12"/>
-    </row>
-    <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="12"/>
-      <c r="B179" s="12"/>
-    </row>
-    <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="12"/>
-      <c r="B180" s="12"/>
-    </row>
-    <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="12"/>
-      <c r="B181" s="12"/>
-    </row>
-    <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="12"/>
-      <c r="B182" s="12"/>
-    </row>
-    <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="12"/>
-      <c r="B183" s="12"/>
-    </row>
-    <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="12"/>
-      <c r="B184" s="12"/>
-    </row>
-    <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="12"/>
-      <c r="B185" s="12"/>
-    </row>
-    <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="12"/>
-      <c r="B186" s="12"/>
-    </row>
-    <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="12"/>
-      <c r="B187" s="12"/>
-    </row>
-    <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="12"/>
-      <c r="B188" s="12"/>
-    </row>
-    <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="12"/>
-      <c r="B189" s="12"/>
-    </row>
-    <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="12"/>
-      <c r="B190" s="12"/>
-    </row>
-    <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="12"/>
-      <c r="B191" s="12"/>
-    </row>
-    <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="12"/>
-      <c r="B192" s="12"/>
-    </row>
-    <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="12"/>
-      <c r="B193" s="12"/>
-    </row>
-    <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="12"/>
-      <c r="B194" s="12"/>
-    </row>
-    <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="12"/>
-      <c r="B195" s="12"/>
-    </row>
-    <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="12"/>
-      <c r="B196" s="12"/>
-    </row>
-    <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="12"/>
-      <c r="B197" s="12"/>
-    </row>
-    <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="12"/>
-      <c r="B198" s="12"/>
-    </row>
-    <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="12"/>
-      <c r="B199" s="12"/>
-    </row>
-    <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="12"/>
-      <c r="B200" s="12"/>
-    </row>
-    <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="12"/>
-      <c r="B201" s="12"/>
-    </row>
-    <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="12"/>
-      <c r="B202" s="12"/>
-    </row>
+      <c r="A165" s="15"/>
+      <c r="B165" s="15"/>
+    </row>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
     <row r="203" ht="15.75" customHeight="1"/>
     <row r="204" ht="15.75" customHeight="1"/>
     <row r="205" ht="15.75" customHeight="1"/>
@@ -2558,50 +3250,18 @@
     <row r="941" ht="15.75" customHeight="1"/>
     <row r="942" ht="15.75" customHeight="1"/>
     <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
   </sheetData>
-  <conditionalFormatting sqref="I2:I980">
+  <autoFilter ref="$M$1:$T$11">
+    <sortState ref="M1:T11">
+      <sortCondition ref="M1:M11"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="I2:I943">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C2="home"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:H980">
+  <conditionalFormatting sqref="F2:H943">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>$C2="away"</formula>
     </cfRule>

--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yasif\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0283A9FE-AD0A-4935-BEED-D410226A4B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31AD42DB-C896-49C5-AA5C-7B620F71211C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Volunteers_table" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Volunteers_table!$L$1:$R$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Volunteers_table!$J$1:$O$11</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
   <si>
     <t>Game</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>Away</t>
-  </si>
-  <si>
-    <t>—</t>
   </si>
   <si>
     <t>Amit A</t>
@@ -123,7 +120,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -160,10 +157,24 @@
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
-      <i/>
       <sz val="10"/>
-      <color rgb="FF1F1F1F"/>
-      <name val="&quot;Google Sans Text&quot;"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -219,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -227,43 +238,26 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -494,7 +488,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:R944"/>
+  <dimension ref="A1:O944"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -502,12 +496,11 @@
     <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="5" width="12.5703125" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="9" max="9" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="3.42578125" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" customWidth="1"/>
+    <col min="8" max="9" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15.75" customHeight="1">
+    <row r="1" spans="1:15" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -532,471 +525,422 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="M1" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A2" s="8">
+        <v>1</v>
+      </c>
+      <c r="B2" s="9">
+        <v>46256</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="4">
+        <f>COUNTIF(E$2:E$964,$J2)</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <f>COUNTIF(F$2:F$964,$J2)</f>
+        <v>1</v>
+      </c>
+      <c r="M2" s="4">
+        <f>COUNTIF(G$2:G$964,$J2)</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <f>COUNTIF(H$2:H$964,$J2)</f>
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <f>SUM(K2:N2)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A3" s="8">
         <v>4</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="B3" s="9">
+        <v>46263</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="5"/>
+      <c r="J3" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="4">
+        <f>COUNTIF(E$2:E$964,$J3)</f>
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <f>COUNTIF(F$2:F$964,$J3)</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="4">
+        <f>COUNTIF(G$2:G$964,$J3)</f>
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <f>COUNTIF(H$2:H$964,$J3)</f>
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <f>SUM(K3:N3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A4" s="8">
         <v>5</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="B4" s="9">
+        <v>46270</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="4">
+        <f>COUNTIF(E$2:E$964,$J4)</f>
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <f>COUNTIF(F$2:F$964,$J4)</f>
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <f>COUNTIF(G$2:G$964,$J4)</f>
+        <v>1</v>
+      </c>
+      <c r="N4" s="4">
+        <f>COUNTIF(H$2:H$964,$J4)</f>
+        <v>1</v>
+      </c>
+      <c r="O4" s="4">
+        <f>SUM(K4:N4)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A5" s="8">
         <v>6</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="B5" s="9">
+        <v>46277</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="5"/>
+      <c r="J5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="4">
+        <f>COUNTIF(E$2:E$964,$J5)</f>
+        <v>0</v>
+      </c>
+      <c r="L5" s="4">
+        <f>COUNTIF(F$2:F$964,$J5)</f>
+        <v>1</v>
+      </c>
+      <c r="M5" s="4">
+        <f>COUNTIF(G$2:G$964,$J5)</f>
+        <v>1</v>
+      </c>
+      <c r="N5" s="4">
+        <f>COUNTIF(H$2:H$964,$J5)</f>
+        <v>0</v>
+      </c>
+      <c r="O5" s="4">
+        <f>SUM(K5:N5)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A6" s="8">
         <v>7</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="B6" s="9">
+        <v>46284</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="4">
+        <f>COUNTIF(E$2:E$964,$J6)</f>
+        <v>1</v>
+      </c>
+      <c r="L6" s="4">
+        <f>COUNTIF(F$2:F$964,$J6)</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="4">
+        <f>COUNTIF(G$2:G$964,$J6)</f>
+        <v>1</v>
+      </c>
+      <c r="N6" s="4">
+        <f>COUNTIF(H$2:H$964,$J6)</f>
+        <v>0</v>
+      </c>
+      <c r="O6" s="4">
+        <f>SUM(K6:N6)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A7" s="8">
+        <v>8</v>
+      </c>
+      <c r="B7" s="9">
+        <v>46291</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="5"/>
+      <c r="J7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="4">
+        <f>COUNTIF(E$2:E$964,$J7)</f>
+        <v>1</v>
+      </c>
+      <c r="L7" s="4">
+        <f>COUNTIF(F$2:F$964,$J7)</f>
+        <v>0</v>
+      </c>
+      <c r="M7" s="4">
+        <f>COUNTIF(G$2:G$964,$J7)</f>
+        <v>0</v>
+      </c>
+      <c r="N7" s="4">
+        <f>COUNTIF(H$2:H$964,$J7)</f>
+        <v>0</v>
+      </c>
+      <c r="O7" s="4">
+        <f>SUM(K7:N7)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A8" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A2" s="5">
+      <c r="B8" s="9">
+        <v>46298</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H8" s="5"/>
+      <c r="J8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="4">
+        <f>COUNTIF(E$2:E$964,$J8)</f>
         <v>1</v>
       </c>
-      <c r="B2" s="6">
-        <v>46256</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="9" t="s">
+      <c r="L8" s="4">
+        <f>COUNTIF(F$2:F$964,$J8)</f>
+        <v>1</v>
+      </c>
+      <c r="M8" s="4">
+        <f>COUNTIF(G$2:G$964,$J8)</f>
+        <v>0</v>
+      </c>
+      <c r="N8" s="4">
+        <f>COUNTIF(H$2:H$964,$J8)</f>
+        <v>0</v>
+      </c>
+      <c r="O8" s="4">
+        <f>SUM(K8:N8)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <c r="J9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="4">
+        <f>COUNTIF(E$2:E$964,$J9)</f>
+        <v>0</v>
+      </c>
+      <c r="L9" s="4">
+        <f>COUNTIF(F$2:F$964,$J9)</f>
+        <v>0</v>
+      </c>
+      <c r="M9" s="4">
+        <f>COUNTIF(G$2:G$964,$J9)</f>
+        <v>1</v>
+      </c>
+      <c r="N9" s="4">
+        <f>COUNTIF(H$2:H$964,$J9)</f>
+        <v>0</v>
+      </c>
+      <c r="O9" s="4">
+        <f>SUM(K9:N9)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <c r="J10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="4">
+        <f>COUNTIF(E$2:E$964,$J10)</f>
+        <v>0</v>
+      </c>
+      <c r="L10" s="4">
+        <f>COUNTIF(F$2:F$964,$J10)</f>
+        <v>0</v>
+      </c>
+      <c r="M10" s="4">
+        <f>COUNTIF(G$2:G$964,$J10)</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="4">
+        <f>COUNTIF(H$2:H$964,$J10)</f>
+        <v>1</v>
+      </c>
+      <c r="O10" s="4">
+        <f>SUM(K10:N10)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="J11" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M2" s="4">
-        <f>COUNTIF(D$2:D$964,$L2)</f>
-        <v>0</v>
-      </c>
-      <c r="N2" s="4">
-        <f>COUNTIF(E$2:E$964,$L2)</f>
-        <v>0</v>
-      </c>
-      <c r="O2" s="4">
-        <f>COUNTIF(F$2:F$964,$L2)</f>
+      <c r="K11" s="4">
+        <f>COUNTIF(E$2:E$964,$J11)</f>
         <v>1</v>
       </c>
-      <c r="P2" s="4">
-        <f>COUNTIF(G$2:G$964,$L2)</f>
-        <v>0</v>
-      </c>
-      <c r="Q2" s="4">
-        <f>COUNTIF(H$2:H$964,$L2)</f>
-        <v>0</v>
-      </c>
-      <c r="R2" s="4">
-        <f t="shared" ref="R2:R12" si="0">SUM(M2:Q2)</f>
+      <c r="L11" s="4">
+        <f>COUNTIF(F$2:F$964,$J11)</f>
+        <v>0</v>
+      </c>
+      <c r="M11" s="4">
+        <f>COUNTIF(G$2:G$964,$J11)</f>
+        <v>0</v>
+      </c>
+      <c r="N11" s="4">
+        <f>COUNTIF(H$2:H$964,$J11)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A3" s="5">
-        <v>4</v>
-      </c>
-      <c r="B3" s="6">
-        <v>46263</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="12"/>
-      <c r="H3" s="14"/>
-      <c r="L3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M3" s="4">
-        <f>COUNTIF(D$2:D$964,$L3)</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <f>COUNTIF(E$2:E$964,$L3)</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="4">
-        <f>COUNTIF(F$2:F$964,$L3)</f>
-        <v>0</v>
-      </c>
-      <c r="P3" s="4">
-        <f>COUNTIF(G$2:G$964,$L3)</f>
-        <v>0</v>
-      </c>
-      <c r="Q3" s="4">
-        <f>COUNTIF(H$2:H$964,$L3)</f>
-        <v>0</v>
-      </c>
-      <c r="R3" s="4">
-        <f>SUM(M3:Q3)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A4" s="5">
-        <v>5</v>
-      </c>
-      <c r="B4" s="6">
-        <v>46270</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="M4" s="4">
-        <f>COUNTIF(D$2:D$964,$L4)</f>
-        <v>0</v>
-      </c>
-      <c r="N4" s="4">
-        <f>COUNTIF(E$2:E$964,$L4)</f>
-        <v>0</v>
-      </c>
-      <c r="O4" s="4">
-        <f>COUNTIF(F$2:F$964,$L4)</f>
-        <v>0</v>
-      </c>
-      <c r="P4" s="4">
-        <f>COUNTIF(G$2:G$964,$L4)</f>
-        <v>1</v>
-      </c>
-      <c r="Q4" s="4">
-        <f>COUNTIF(H$2:H$964,$L4)</f>
-        <v>1</v>
-      </c>
-      <c r="R4" s="4">
-        <f>SUM(M4:Q4)</f>
+      <c r="O11" s="4">
+        <f>SUM(K11:N11)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A5" s="5">
-        <v>6</v>
-      </c>
-      <c r="B5" s="6">
-        <v>46277</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M5" s="4">
-        <f>COUNTIF(D$2:D$964,$L5)</f>
-        <v>0</v>
-      </c>
-      <c r="N5" s="4">
-        <f>COUNTIF(E$2:E$964,$L5)</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="4">
-        <f>COUNTIF(F$2:F$964,$L5)</f>
-        <v>1</v>
-      </c>
-      <c r="P5" s="4">
-        <f>COUNTIF(G$2:G$964,$L5)</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="4">
-        <f>COUNTIF(H$2:H$964,$L5)</f>
-        <v>0</v>
-      </c>
-      <c r="R5" s="4">
-        <f>SUM(M5:Q5)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A6" s="5">
-        <v>7</v>
-      </c>
-      <c r="B6" s="6">
-        <v>46284</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
-      <c r="H6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="M6" s="4">
-        <f>COUNTIF(D$2:D$964,$L6)</f>
-        <v>0</v>
-      </c>
-      <c r="N6" s="4">
-        <f>COUNTIF(E$2:E$964,$L6)</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="4">
-        <f>COUNTIF(F$2:F$964,$L6)</f>
-        <v>1</v>
-      </c>
-      <c r="P6" s="4">
-        <f>COUNTIF(G$2:G$964,$L6)</f>
-        <v>1</v>
-      </c>
-      <c r="Q6" s="4">
-        <f>COUNTIF(H$2:H$964,$L6)</f>
-        <v>0</v>
-      </c>
-      <c r="R6" s="4">
-        <f>SUM(M6:Q6)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A7" s="5">
-        <v>8</v>
-      </c>
-      <c r="B7" s="6">
-        <v>46291</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="9"/>
-      <c r="L7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" s="4">
-        <f>COUNTIF(D$2:D$964,$L7)</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="4">
-        <f>COUNTIF(E$2:E$964,$L7)</f>
-        <v>1</v>
-      </c>
-      <c r="O7" s="4">
-        <f>COUNTIF(F$2:F$964,$L7)</f>
-        <v>0</v>
-      </c>
-      <c r="P7" s="4">
-        <f>COUNTIF(G$2:G$964,$L7)</f>
-        <v>0</v>
-      </c>
-      <c r="Q7" s="4">
-        <f>COUNTIF(H$2:H$964,$L7)</f>
-        <v>0</v>
-      </c>
-      <c r="R7" s="4">
-        <f>SUM(M7:Q7)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A8" s="5">
-        <v>9</v>
-      </c>
-      <c r="B8" s="6">
-        <v>46298</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="8"/>
-      <c r="L8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="M8" s="4">
-        <f>COUNTIF(D$2:D$964,$L8)</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="4">
-        <f>COUNTIF(E$2:E$964,$L8)</f>
-        <v>2</v>
-      </c>
-      <c r="O8" s="4">
-        <f>COUNTIF(F$2:F$964,$L8)</f>
-        <v>0</v>
-      </c>
-      <c r="P8" s="4">
-        <f>COUNTIF(G$2:G$964,$L8)</f>
-        <v>0</v>
-      </c>
-      <c r="Q8" s="4">
-        <f>COUNTIF(H$2:H$964,$L8)</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="4">
-        <f>SUM(M8:Q8)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="15.75" customHeight="1">
-      <c r="L9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="4">
-        <f>COUNTIF(D$2:D$964,$L9)</f>
-        <v>0</v>
-      </c>
-      <c r="N9" s="4">
-        <f>COUNTIF(E$2:E$964,$L9)</f>
-        <v>0</v>
-      </c>
-      <c r="O9" s="4">
-        <f>COUNTIF(F$2:F$964,$L9)</f>
-        <v>0</v>
-      </c>
-      <c r="P9" s="4">
-        <f>COUNTIF(G$2:G$964,$L9)</f>
-        <v>1</v>
-      </c>
-      <c r="Q9" s="4">
-        <f>COUNTIF(H$2:H$964,$L9)</f>
-        <v>0</v>
-      </c>
-      <c r="R9" s="4">
-        <f>SUM(M9:Q9)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1">
-      <c r="L10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="M10" s="4">
-        <f>COUNTIF(D$2:D$964,$L10)</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="4">
-        <f>COUNTIF(E$2:E$964,$L10)</f>
-        <v>0</v>
-      </c>
-      <c r="O10" s="4">
-        <f>COUNTIF(F$2:F$964,$L10)</f>
-        <v>1</v>
-      </c>
-      <c r="P10" s="4">
-        <f>COUNTIF(G$2:G$964,$L10)</f>
-        <v>0</v>
-      </c>
-      <c r="Q10" s="4">
-        <f>COUNTIF(H$2:H$964,$L10)</f>
-        <v>1</v>
-      </c>
-      <c r="R10" s="4">
-        <f>SUM(M10:Q10)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="15.75" customHeight="1">
-      <c r="L11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="M11" s="4">
-        <f>COUNTIF(D$2:D$964,$L11)</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="4">
-        <f>COUNTIF(E$2:E$964,$L11)</f>
-        <v>1</v>
-      </c>
-      <c r="O11" s="4">
-        <f>COUNTIF(F$2:F$964,$L11)</f>
-        <v>0</v>
-      </c>
-      <c r="P11" s="4">
-        <f>COUNTIF(G$2:G$964,$L11)</f>
-        <v>0</v>
-      </c>
-      <c r="Q11" s="4">
-        <f>COUNTIF(H$2:H$964,$L11)</f>
-        <v>1</v>
-      </c>
-      <c r="R11" s="4">
-        <f>SUM(M11:Q11)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="15.75" customHeight="1"/>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1"/>
-    <row r="14" spans="1:18" ht="15.75" customHeight="1"/>
-    <row r="15" spans="1:18" ht="15.75" customHeight="1"/>
-    <row r="16" spans="1:18" ht="15.75" customHeight="1"/>
+    <row r="12" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="13" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="14" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="15" spans="1:15" ht="15.75" customHeight="1"/>
+    <row r="16" spans="1:15" ht="15.75" customHeight="1"/>
     <row r="17" ht="15.75" customHeight="1"/>
     <row r="18" ht="15.75" customHeight="1"/>
     <row r="19" ht="15.75" customHeight="1"/>
@@ -1024,500 +968,500 @@
     <row r="41" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="42" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="43" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A43" s="11"/>
-      <c r="B43" s="11"/>
+      <c r="A43" s="6"/>
+      <c r="B43" s="6"/>
     </row>
     <row r="44" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A44" s="11"/>
-      <c r="B44" s="11"/>
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
     </row>
     <row r="45" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A45" s="11"/>
-      <c r="B45" s="11"/>
+      <c r="A45" s="6"/>
+      <c r="B45" s="6"/>
     </row>
     <row r="46" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A46" s="11"/>
-      <c r="B46" s="11"/>
+      <c r="A46" s="6"/>
+      <c r="B46" s="6"/>
     </row>
     <row r="47" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A47" s="11"/>
-      <c r="B47" s="11"/>
+      <c r="A47" s="6"/>
+      <c r="B47" s="6"/>
     </row>
     <row r="48" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
+      <c r="A48" s="6"/>
+      <c r="B48" s="6"/>
     </row>
     <row r="49" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A49" s="11"/>
-      <c r="B49" s="11"/>
+      <c r="A49" s="6"/>
+      <c r="B49" s="6"/>
     </row>
     <row r="50" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A50" s="11"/>
-      <c r="B50" s="11"/>
+      <c r="A50" s="6"/>
+      <c r="B50" s="6"/>
     </row>
     <row r="51" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A51" s="11"/>
-      <c r="B51" s="11"/>
+      <c r="A51" s="6"/>
+      <c r="B51" s="6"/>
     </row>
     <row r="52" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A52" s="11"/>
-      <c r="B52" s="11"/>
+      <c r="A52" s="6"/>
+      <c r="B52" s="6"/>
     </row>
     <row r="53" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A53" s="11"/>
-      <c r="B53" s="11"/>
+      <c r="A53" s="6"/>
+      <c r="B53" s="6"/>
     </row>
     <row r="54" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A54" s="11"/>
-      <c r="B54" s="11"/>
+      <c r="A54" s="6"/>
+      <c r="B54" s="6"/>
     </row>
     <row r="55" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A55" s="11"/>
-      <c r="B55" s="11"/>
+      <c r="A55" s="6"/>
+      <c r="B55" s="6"/>
     </row>
     <row r="56" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A56" s="11"/>
-      <c r="B56" s="11"/>
+      <c r="A56" s="6"/>
+      <c r="B56" s="6"/>
     </row>
     <row r="57" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A57" s="11"/>
-      <c r="B57" s="11"/>
+      <c r="A57" s="6"/>
+      <c r="B57" s="6"/>
     </row>
     <row r="58" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A58" s="11"/>
-      <c r="B58" s="11"/>
+      <c r="A58" s="6"/>
+      <c r="B58" s="6"/>
     </row>
     <row r="59" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A59" s="11"/>
-      <c r="B59" s="11"/>
+      <c r="A59" s="6"/>
+      <c r="B59" s="6"/>
     </row>
     <row r="60" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A60" s="11"/>
-      <c r="B60" s="11"/>
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
     </row>
     <row r="61" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A61" s="11"/>
-      <c r="B61" s="11"/>
+      <c r="A61" s="6"/>
+      <c r="B61" s="6"/>
     </row>
     <row r="62" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A62" s="11"/>
-      <c r="B62" s="11"/>
+      <c r="A62" s="6"/>
+      <c r="B62" s="6"/>
     </row>
     <row r="63" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A63" s="11"/>
-      <c r="B63" s="11"/>
+      <c r="A63" s="6"/>
+      <c r="B63" s="6"/>
     </row>
     <row r="64" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A64" s="11"/>
-      <c r="B64" s="11"/>
+      <c r="A64" s="6"/>
+      <c r="B64" s="6"/>
     </row>
     <row r="65" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
+      <c r="A65" s="6"/>
+      <c r="B65" s="6"/>
     </row>
     <row r="66" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A66" s="11"/>
-      <c r="B66" s="11"/>
+      <c r="A66" s="6"/>
+      <c r="B66" s="6"/>
     </row>
     <row r="67" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A67" s="11"/>
-      <c r="B67" s="11"/>
+      <c r="A67" s="6"/>
+      <c r="B67" s="6"/>
     </row>
     <row r="68" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A68" s="11"/>
-      <c r="B68" s="11"/>
+      <c r="A68" s="6"/>
+      <c r="B68" s="6"/>
     </row>
     <row r="69" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A69" s="11"/>
-      <c r="B69" s="11"/>
+      <c r="A69" s="6"/>
+      <c r="B69" s="6"/>
     </row>
     <row r="70" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A70" s="11"/>
-      <c r="B70" s="11"/>
+      <c r="A70" s="6"/>
+      <c r="B70" s="6"/>
     </row>
     <row r="71" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A71" s="11"/>
-      <c r="B71" s="11"/>
+      <c r="A71" s="6"/>
+      <c r="B71" s="6"/>
     </row>
     <row r="72" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A72" s="11"/>
-      <c r="B72" s="11"/>
+      <c r="A72" s="6"/>
+      <c r="B72" s="6"/>
     </row>
     <row r="73" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A73" s="11"/>
-      <c r="B73" s="11"/>
+      <c r="A73" s="6"/>
+      <c r="B73" s="6"/>
     </row>
     <row r="74" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A74" s="11"/>
-      <c r="B74" s="11"/>
+      <c r="A74" s="6"/>
+      <c r="B74" s="6"/>
     </row>
     <row r="75" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A75" s="11"/>
-      <c r="B75" s="11"/>
+      <c r="A75" s="6"/>
+      <c r="B75" s="6"/>
     </row>
     <row r="76" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A76" s="11"/>
-      <c r="B76" s="11"/>
+      <c r="A76" s="6"/>
+      <c r="B76" s="6"/>
     </row>
     <row r="77" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A77" s="11"/>
-      <c r="B77" s="11"/>
+      <c r="A77" s="6"/>
+      <c r="B77" s="6"/>
     </row>
     <row r="78" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A78" s="11"/>
-      <c r="B78" s="11"/>
+      <c r="A78" s="6"/>
+      <c r="B78" s="6"/>
     </row>
     <row r="79" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A79" s="11"/>
-      <c r="B79" s="11"/>
+      <c r="A79" s="6"/>
+      <c r="B79" s="6"/>
     </row>
     <row r="80" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A80" s="11"/>
-      <c r="B80" s="11"/>
+      <c r="A80" s="6"/>
+      <c r="B80" s="6"/>
     </row>
     <row r="81" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A81" s="11"/>
-      <c r="B81" s="11"/>
+      <c r="A81" s="6"/>
+      <c r="B81" s="6"/>
     </row>
     <row r="82" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A82" s="11"/>
-      <c r="B82" s="11"/>
+      <c r="A82" s="6"/>
+      <c r="B82" s="6"/>
     </row>
     <row r="83" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A83" s="11"/>
-      <c r="B83" s="11"/>
+      <c r="A83" s="6"/>
+      <c r="B83" s="6"/>
     </row>
     <row r="84" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A84" s="11"/>
-      <c r="B84" s="11"/>
+      <c r="A84" s="6"/>
+      <c r="B84" s="6"/>
     </row>
     <row r="85" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A85" s="11"/>
-      <c r="B85" s="11"/>
+      <c r="A85" s="6"/>
+      <c r="B85" s="6"/>
     </row>
     <row r="86" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A86" s="11"/>
-      <c r="B86" s="11"/>
+      <c r="A86" s="6"/>
+      <c r="B86" s="6"/>
     </row>
     <row r="87" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A87" s="11"/>
-      <c r="B87" s="11"/>
+      <c r="A87" s="6"/>
+      <c r="B87" s="6"/>
     </row>
     <row r="88" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A88" s="11"/>
-      <c r="B88" s="11"/>
+      <c r="A88" s="6"/>
+      <c r="B88" s="6"/>
     </row>
     <row r="89" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A89" s="11"/>
-      <c r="B89" s="11"/>
+      <c r="A89" s="6"/>
+      <c r="B89" s="6"/>
     </row>
     <row r="90" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A90" s="11"/>
-      <c r="B90" s="11"/>
+      <c r="A90" s="6"/>
+      <c r="B90" s="6"/>
     </row>
     <row r="91" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A91" s="11"/>
-      <c r="B91" s="11"/>
+      <c r="A91" s="6"/>
+      <c r="B91" s="6"/>
     </row>
     <row r="92" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A92" s="11"/>
-      <c r="B92" s="11"/>
+      <c r="A92" s="6"/>
+      <c r="B92" s="6"/>
     </row>
     <row r="93" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A93" s="11"/>
-      <c r="B93" s="11"/>
+      <c r="A93" s="6"/>
+      <c r="B93" s="6"/>
     </row>
     <row r="94" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A94" s="11"/>
-      <c r="B94" s="11"/>
+      <c r="A94" s="6"/>
+      <c r="B94" s="6"/>
     </row>
     <row r="95" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A95" s="11"/>
-      <c r="B95" s="11"/>
+      <c r="A95" s="6"/>
+      <c r="B95" s="6"/>
     </row>
     <row r="96" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A96" s="11"/>
-      <c r="B96" s="11"/>
+      <c r="A96" s="6"/>
+      <c r="B96" s="6"/>
     </row>
     <row r="97" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A97" s="11"/>
-      <c r="B97" s="11"/>
+      <c r="A97" s="6"/>
+      <c r="B97" s="6"/>
     </row>
     <row r="98" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A98" s="11"/>
-      <c r="B98" s="11"/>
+      <c r="A98" s="6"/>
+      <c r="B98" s="6"/>
     </row>
     <row r="99" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A99" s="11"/>
-      <c r="B99" s="11"/>
+      <c r="A99" s="6"/>
+      <c r="B99" s="6"/>
     </row>
     <row r="100" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A100" s="11"/>
-      <c r="B100" s="11"/>
+      <c r="A100" s="6"/>
+      <c r="B100" s="6"/>
     </row>
     <row r="101" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A101" s="11"/>
-      <c r="B101" s="11"/>
+      <c r="A101" s="6"/>
+      <c r="B101" s="6"/>
     </row>
     <row r="102" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A102" s="11"/>
-      <c r="B102" s="11"/>
+      <c r="A102" s="6"/>
+      <c r="B102" s="6"/>
     </row>
     <row r="103" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A103" s="11"/>
-      <c r="B103" s="11"/>
+      <c r="A103" s="6"/>
+      <c r="B103" s="6"/>
     </row>
     <row r="104" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A104" s="11"/>
-      <c r="B104" s="11"/>
+      <c r="A104" s="6"/>
+      <c r="B104" s="6"/>
     </row>
     <row r="105" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A105" s="11"/>
-      <c r="B105" s="11"/>
+      <c r="A105" s="6"/>
+      <c r="B105" s="6"/>
     </row>
     <row r="106" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A106" s="11"/>
-      <c r="B106" s="11"/>
+      <c r="A106" s="6"/>
+      <c r="B106" s="6"/>
     </row>
     <row r="107" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A107" s="11"/>
-      <c r="B107" s="11"/>
+      <c r="A107" s="6"/>
+      <c r="B107" s="6"/>
     </row>
     <row r="108" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A108" s="11"/>
-      <c r="B108" s="11"/>
+      <c r="A108" s="6"/>
+      <c r="B108" s="6"/>
     </row>
     <row r="109" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A109" s="11"/>
-      <c r="B109" s="11"/>
+      <c r="A109" s="6"/>
+      <c r="B109" s="6"/>
     </row>
     <row r="110" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A110" s="11"/>
-      <c r="B110" s="11"/>
+      <c r="A110" s="6"/>
+      <c r="B110" s="6"/>
     </row>
     <row r="111" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A111" s="11"/>
-      <c r="B111" s="11"/>
+      <c r="A111" s="6"/>
+      <c r="B111" s="6"/>
     </row>
     <row r="112" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A112" s="11"/>
-      <c r="B112" s="11"/>
+      <c r="A112" s="6"/>
+      <c r="B112" s="6"/>
     </row>
     <row r="113" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A113" s="11"/>
-      <c r="B113" s="11"/>
+      <c r="A113" s="6"/>
+      <c r="B113" s="6"/>
     </row>
     <row r="114" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A114" s="11"/>
-      <c r="B114" s="11"/>
+      <c r="A114" s="6"/>
+      <c r="B114" s="6"/>
     </row>
     <row r="115" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A115" s="11"/>
-      <c r="B115" s="11"/>
+      <c r="A115" s="6"/>
+      <c r="B115" s="6"/>
     </row>
     <row r="116" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A116" s="11"/>
-      <c r="B116" s="11"/>
+      <c r="A116" s="6"/>
+      <c r="B116" s="6"/>
     </row>
     <row r="117" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A117" s="11"/>
-      <c r="B117" s="11"/>
+      <c r="A117" s="6"/>
+      <c r="B117" s="6"/>
     </row>
     <row r="118" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A118" s="11"/>
-      <c r="B118" s="11"/>
+      <c r="A118" s="6"/>
+      <c r="B118" s="6"/>
     </row>
     <row r="119" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A119" s="11"/>
-      <c r="B119" s="11"/>
+      <c r="A119" s="6"/>
+      <c r="B119" s="6"/>
     </row>
     <row r="120" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A120" s="11"/>
-      <c r="B120" s="11"/>
+      <c r="A120" s="6"/>
+      <c r="B120" s="6"/>
     </row>
     <row r="121" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A121" s="11"/>
-      <c r="B121" s="11"/>
+      <c r="A121" s="6"/>
+      <c r="B121" s="6"/>
     </row>
     <row r="122" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A122" s="11"/>
-      <c r="B122" s="11"/>
+      <c r="A122" s="6"/>
+      <c r="B122" s="6"/>
     </row>
     <row r="123" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A123" s="11"/>
-      <c r="B123" s="11"/>
+      <c r="A123" s="6"/>
+      <c r="B123" s="6"/>
     </row>
     <row r="124" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A124" s="11"/>
-      <c r="B124" s="11"/>
+      <c r="A124" s="6"/>
+      <c r="B124" s="6"/>
     </row>
     <row r="125" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A125" s="11"/>
-      <c r="B125" s="11"/>
+      <c r="A125" s="6"/>
+      <c r="B125" s="6"/>
     </row>
     <row r="126" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A126" s="11"/>
-      <c r="B126" s="11"/>
+      <c r="A126" s="6"/>
+      <c r="B126" s="6"/>
     </row>
     <row r="127" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A127" s="11"/>
-      <c r="B127" s="11"/>
+      <c r="A127" s="6"/>
+      <c r="B127" s="6"/>
     </row>
     <row r="128" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A128" s="11"/>
-      <c r="B128" s="11"/>
+      <c r="A128" s="6"/>
+      <c r="B128" s="6"/>
     </row>
     <row r="129" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A129" s="11"/>
-      <c r="B129" s="11"/>
+      <c r="A129" s="6"/>
+      <c r="B129" s="6"/>
     </row>
     <row r="130" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A130" s="11"/>
-      <c r="B130" s="11"/>
+      <c r="A130" s="6"/>
+      <c r="B130" s="6"/>
     </row>
     <row r="131" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A131" s="11"/>
-      <c r="B131" s="11"/>
+      <c r="A131" s="6"/>
+      <c r="B131" s="6"/>
     </row>
     <row r="132" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A132" s="11"/>
-      <c r="B132" s="11"/>
+      <c r="A132" s="6"/>
+      <c r="B132" s="6"/>
     </row>
     <row r="133" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A133" s="11"/>
-      <c r="B133" s="11"/>
+      <c r="A133" s="6"/>
+      <c r="B133" s="6"/>
     </row>
     <row r="134" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A134" s="11"/>
-      <c r="B134" s="11"/>
+      <c r="A134" s="6"/>
+      <c r="B134" s="6"/>
     </row>
     <row r="135" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A135" s="11"/>
-      <c r="B135" s="11"/>
+      <c r="A135" s="6"/>
+      <c r="B135" s="6"/>
     </row>
     <row r="136" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A136" s="11"/>
-      <c r="B136" s="11"/>
+      <c r="A136" s="6"/>
+      <c r="B136" s="6"/>
     </row>
     <row r="137" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A137" s="11"/>
-      <c r="B137" s="11"/>
+      <c r="A137" s="6"/>
+      <c r="B137" s="6"/>
     </row>
     <row r="138" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A138" s="11"/>
-      <c r="B138" s="11"/>
+      <c r="A138" s="6"/>
+      <c r="B138" s="6"/>
     </row>
     <row r="139" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A139" s="11"/>
-      <c r="B139" s="11"/>
+      <c r="A139" s="6"/>
+      <c r="B139" s="6"/>
     </row>
     <row r="140" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A140" s="11"/>
-      <c r="B140" s="11"/>
+      <c r="A140" s="6"/>
+      <c r="B140" s="6"/>
     </row>
     <row r="141" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A141" s="11"/>
-      <c r="B141" s="11"/>
+      <c r="A141" s="6"/>
+      <c r="B141" s="6"/>
     </row>
     <row r="142" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A142" s="11"/>
-      <c r="B142" s="11"/>
+      <c r="A142" s="6"/>
+      <c r="B142" s="6"/>
     </row>
     <row r="143" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A143" s="11"/>
-      <c r="B143" s="11"/>
+      <c r="A143" s="6"/>
+      <c r="B143" s="6"/>
     </row>
     <row r="144" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A144" s="11"/>
-      <c r="B144" s="11"/>
+      <c r="A144" s="6"/>
+      <c r="B144" s="6"/>
     </row>
     <row r="145" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A145" s="11"/>
-      <c r="B145" s="11"/>
+      <c r="A145" s="6"/>
+      <c r="B145" s="6"/>
     </row>
     <row r="146" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A146" s="11"/>
-      <c r="B146" s="11"/>
+      <c r="A146" s="6"/>
+      <c r="B146" s="6"/>
     </row>
     <row r="147" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A147" s="11"/>
-      <c r="B147" s="11"/>
+      <c r="A147" s="6"/>
+      <c r="B147" s="6"/>
     </row>
     <row r="148" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A148" s="11"/>
-      <c r="B148" s="11"/>
+      <c r="A148" s="6"/>
+      <c r="B148" s="6"/>
     </row>
     <row r="149" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A149" s="11"/>
-      <c r="B149" s="11"/>
+      <c r="A149" s="6"/>
+      <c r="B149" s="6"/>
     </row>
     <row r="150" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A150" s="11"/>
-      <c r="B150" s="11"/>
+      <c r="A150" s="6"/>
+      <c r="B150" s="6"/>
     </row>
     <row r="151" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A151" s="11"/>
-      <c r="B151" s="11"/>
+      <c r="A151" s="6"/>
+      <c r="B151" s="6"/>
     </row>
     <row r="152" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A152" s="11"/>
-      <c r="B152" s="11"/>
+      <c r="A152" s="6"/>
+      <c r="B152" s="6"/>
     </row>
     <row r="153" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A153" s="11"/>
-      <c r="B153" s="11"/>
+      <c r="A153" s="6"/>
+      <c r="B153" s="6"/>
     </row>
     <row r="154" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A154" s="11"/>
-      <c r="B154" s="11"/>
+      <c r="A154" s="6"/>
+      <c r="B154" s="6"/>
     </row>
     <row r="155" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A155" s="11"/>
-      <c r="B155" s="11"/>
+      <c r="A155" s="6"/>
+      <c r="B155" s="6"/>
     </row>
     <row r="156" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A156" s="11"/>
-      <c r="B156" s="11"/>
+      <c r="A156" s="6"/>
+      <c r="B156" s="6"/>
     </row>
     <row r="157" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A157" s="11"/>
-      <c r="B157" s="11"/>
+      <c r="A157" s="6"/>
+      <c r="B157" s="6"/>
     </row>
     <row r="158" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A158" s="11"/>
-      <c r="B158" s="11"/>
+      <c r="A158" s="6"/>
+      <c r="B158" s="6"/>
     </row>
     <row r="159" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A159" s="11"/>
-      <c r="B159" s="11"/>
+      <c r="A159" s="6"/>
+      <c r="B159" s="6"/>
     </row>
     <row r="160" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A160" s="11"/>
-      <c r="B160" s="11"/>
+      <c r="A160" s="6"/>
+      <c r="B160" s="6"/>
     </row>
     <row r="161" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A161" s="11"/>
-      <c r="B161" s="11"/>
+      <c r="A161" s="6"/>
+      <c r="B161" s="6"/>
     </row>
     <row r="162" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A162" s="11"/>
-      <c r="B162" s="11"/>
+      <c r="A162" s="6"/>
+      <c r="B162" s="6"/>
     </row>
     <row r="163" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A163" s="11"/>
-      <c r="B163" s="11"/>
+      <c r="A163" s="6"/>
+      <c r="B163" s="6"/>
     </row>
     <row r="164" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A164" s="11"/>
-      <c r="B164" s="11"/>
+      <c r="A164" s="6"/>
+      <c r="B164" s="6"/>
     </row>
     <row r="165" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A165" s="11"/>
-      <c r="B165" s="11"/>
+      <c r="A165" s="6"/>
+      <c r="B165" s="6"/>
     </row>
     <row r="166" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A166" s="11"/>
-      <c r="B166" s="11"/>
+      <c r="A166" s="6"/>
+      <c r="B166" s="6"/>
     </row>
     <row r="167" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="168" spans="1:2" ht="15.75" customHeight="1"/>
@@ -2298,14 +2242,14 @@
     <row r="943" ht="15.75" customHeight="1"/>
     <row r="944" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="L1:R12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="E2:G2 E43:G944 E4:G6 F3:G3 E8:G8 F7:G7">
-    <cfRule type="expression" dxfId="3" priority="2">
+  <autoFilter ref="J1:O12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="E2:G2 E4:G6 F7:G7 E8:G8 E43:G944 F3:G3">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>$C2="away"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H2:H8 H43:H944">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>$C2="home"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yasif\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31AD42DB-C896-49C5-AA5C-7B620F71211C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8EFDB0-F596-420C-BBC0-5CAD572B21E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="25">
   <si>
     <t>Game</t>
   </si>
@@ -111,6 +111,9 @@
   </si>
   <si>
     <t>Robert</t>
+  </si>
+  <si>
+    <t>--</t>
   </si>
 </sst>
 </file>
@@ -177,7 +180,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -196,14 +199,8 @@
         <bgColor theme="0"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -226,33 +223,51 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -491,56 +506,52 @@
   <dimension ref="A1:O944"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="5" width="12.5703125" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" customWidth="1"/>
-    <col min="8" max="9" width="12.42578125" customWidth="1"/>
+    <col min="1" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" customWidth="1"/>
     <col min="10" max="10" width="15.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
@@ -557,132 +568,146 @@
       <c r="D2" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="5" t="s">
+      <c r="E2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="F2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="4">
-        <f>COUNTIF(E$2:E$964,$J2)</f>
-        <v>0</v>
-      </c>
-      <c r="L2" s="4">
-        <f>COUNTIF(F$2:F$964,$J2)</f>
+      <c r="K2" s="3">
+        <f>COUNTIF(E$2:E$964,$J2)*2</f>
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
+        <f t="shared" ref="L2:L11" si="0">COUNTIF(F$2:F$964,$J2)</f>
         <v>1</v>
       </c>
-      <c r="M2" s="4">
-        <f>COUNTIF(G$2:G$964,$J2)</f>
-        <v>0</v>
-      </c>
-      <c r="N2" s="4">
-        <f>COUNTIF(H$2:H$964,$J2)</f>
-        <v>0</v>
-      </c>
-      <c r="O2" s="4">
-        <f>SUM(K2:N2)</f>
+      <c r="M2" s="3">
+        <f t="shared" ref="M2:M11" si="1">COUNTIF(G$2:G$964,$J2)</f>
+        <v>0</v>
+      </c>
+      <c r="N2" s="3">
+        <f t="shared" ref="N2:N11" si="2">COUNTIF(H$2:H$964,$J2)</f>
         <v>1</v>
+      </c>
+      <c r="O2" s="3">
+        <f t="shared" ref="O2:O11" si="3">SUM(K2:N2)</f>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="15.75" customHeight="1">
       <c r="A3" s="8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B3" s="9">
-        <v>46263</v>
+        <v>46256</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="J3" s="13" t="s">
+      <c r="E3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K3" s="4">
-        <f>COUNTIF(E$2:E$964,$J3)</f>
-        <v>0</v>
-      </c>
-      <c r="L3" s="4">
-        <f>COUNTIF(F$2:F$964,$J3)</f>
+      <c r="K3" s="3">
+        <f>COUNTIF(E$2:E$964,$J3)*2</f>
+        <v>2</v>
+      </c>
+      <c r="L3" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M3" s="4">
-        <f>COUNTIF(G$2:G$964,$J3)</f>
-        <v>0</v>
-      </c>
-      <c r="N3" s="4">
-        <f>COUNTIF(H$2:H$964,$J3)</f>
-        <v>0</v>
-      </c>
-      <c r="O3" s="4">
-        <f>SUM(K3:N3)</f>
-        <v>1</v>
+      <c r="M3" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O3" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="15.75" customHeight="1">
       <c r="A4" s="8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="9">
-        <v>46270</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>15</v>
+        <v>46256</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>10</v>
       </c>
       <c r="D4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5" t="s">
+      <c r="E4" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="F4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="4">
-        <f>COUNTIF(E$2:E$964,$J4)</f>
-        <v>0</v>
-      </c>
-      <c r="L4" s="4">
-        <f>COUNTIF(F$2:F$964,$J4)</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="4">
-        <f>COUNTIF(G$2:G$964,$J4)</f>
+      <c r="K4" s="3">
+        <f t="shared" ref="K4:K11" si="4">COUNTIF(E$2:E$964,$J4)*2</f>
+        <v>2</v>
+      </c>
+      <c r="L4" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="N4" s="4">
-        <f>COUNTIF(H$2:H$964,$J4)</f>
-        <v>1</v>
-      </c>
-      <c r="O4" s="4">
-        <f>SUM(K4:N4)</f>
-        <v>2</v>
+      <c r="N4" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O4" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.75" customHeight="1">
       <c r="A5" s="8">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="9">
-        <v>46277</v>
+        <v>46263</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>17</v>
@@ -690,89 +715,97 @@
       <c r="D5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="J5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="4">
-        <f>COUNTIF(E$2:E$964,$J5)</f>
-        <v>0</v>
-      </c>
-      <c r="L5" s="4">
-        <f>COUNTIF(F$2:F$964,$J5)</f>
+      <c r="K5" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="L5" s="3">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="M5" s="4">
-        <f>COUNTIF(G$2:G$964,$J5)</f>
-        <v>1</v>
-      </c>
-      <c r="N5" s="4">
-        <f>COUNTIF(H$2:H$964,$J5)</f>
-        <v>0</v>
-      </c>
-      <c r="O5" s="4">
-        <f>SUM(K5:N5)</f>
-        <v>2</v>
+      <c r="M5" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N5" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O5" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="15.75" customHeight="1">
       <c r="A6" s="8">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="9">
-        <v>46284</v>
-      </c>
-      <c r="C6" s="12" t="s">
+        <v>46270</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="E6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K6" s="4">
-        <f>COUNTIF(E$2:E$964,$J6)</f>
+      <c r="K6" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="L6" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="L6" s="4">
-        <f>COUNTIF(F$2:F$964,$J6)</f>
-        <v>0</v>
-      </c>
-      <c r="M6" s="4">
-        <f>COUNTIF(G$2:G$964,$J6)</f>
-        <v>1</v>
-      </c>
-      <c r="N6" s="4">
-        <f>COUNTIF(H$2:H$964,$J6)</f>
-        <v>0</v>
-      </c>
-      <c r="O6" s="4">
-        <f>SUM(K6:N6)</f>
-        <v>2</v>
+      <c r="N6" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="15.75" customHeight="1">
       <c r="A7" s="8">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B7" s="9">
-        <v>46291</v>
+        <v>46277</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>17</v>
@@ -780,160 +813,212 @@
       <c r="D7" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="J7" s="4" t="s">
+      <c r="E7" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="K7" s="4">
-        <f>COUNTIF(E$2:E$964,$J7)</f>
+      <c r="F7" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K7" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="L7" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="3">
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="L7" s="4">
-        <f>COUNTIF(F$2:F$964,$J7)</f>
-        <v>0</v>
-      </c>
-      <c r="M7" s="4">
-        <f>COUNTIF(G$2:G$964,$J7)</f>
-        <v>0</v>
-      </c>
-      <c r="N7" s="4">
-        <f>COUNTIF(H$2:H$964,$J7)</f>
-        <v>0</v>
-      </c>
-      <c r="O7" s="4">
-        <f>SUM(K7:N7)</f>
-        <v>1</v>
+      <c r="N7" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O7" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="15.75" customHeight="1">
       <c r="A8" s="8">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" s="9">
-        <v>46298</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>17</v>
+        <v>46284</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>15</v>
       </c>
       <c r="D8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O8" s="3">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A9" s="8">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9">
+        <v>46291</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N9" s="3">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="O9" s="3">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <c r="A10" s="8">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9">
+        <v>46298</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="3">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="O10" s="3">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <c r="J11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="J8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" s="4">
-        <f>COUNTIF(E$2:E$964,$J8)</f>
+      <c r="K11" s="3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="L11" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="L8" s="4">
-        <f>COUNTIF(F$2:F$964,$J8)</f>
-        <v>1</v>
-      </c>
-      <c r="M8" s="4">
-        <f>COUNTIF(G$2:G$964,$J8)</f>
-        <v>0</v>
-      </c>
-      <c r="N8" s="4">
-        <f>COUNTIF(H$2:H$964,$J8)</f>
-        <v>0</v>
-      </c>
-      <c r="O8" s="4">
-        <f>SUM(K8:N8)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1">
-      <c r="J9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="4">
-        <f>COUNTIF(E$2:E$964,$J9)</f>
-        <v>0</v>
-      </c>
-      <c r="L9" s="4">
-        <f>COUNTIF(F$2:F$964,$J9)</f>
-        <v>0</v>
-      </c>
-      <c r="M9" s="4">
-        <f>COUNTIF(G$2:G$964,$J9)</f>
-        <v>1</v>
-      </c>
-      <c r="N9" s="4">
-        <f>COUNTIF(H$2:H$964,$J9)</f>
-        <v>0</v>
-      </c>
-      <c r="O9" s="4">
-        <f>SUM(K9:N9)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1">
-      <c r="J10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K10" s="4">
-        <f>COUNTIF(E$2:E$964,$J10)</f>
-        <v>0</v>
-      </c>
-      <c r="L10" s="4">
-        <f>COUNTIF(F$2:F$964,$J10)</f>
-        <v>0</v>
-      </c>
-      <c r="M10" s="4">
-        <f>COUNTIF(G$2:G$964,$J10)</f>
-        <v>0</v>
-      </c>
-      <c r="N10" s="4">
-        <f>COUNTIF(H$2:H$964,$J10)</f>
-        <v>1</v>
-      </c>
-      <c r="O10" s="4">
-        <f>SUM(K10:N10)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1">
-      <c r="J11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="4">
-        <f>COUNTIF(E$2:E$964,$J11)</f>
-        <v>1</v>
-      </c>
-      <c r="L11" s="4">
-        <f>COUNTIF(F$2:F$964,$J11)</f>
-        <v>0</v>
-      </c>
-      <c r="M11" s="4">
-        <f>COUNTIF(G$2:G$964,$J11)</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="4">
-        <f>COUNTIF(H$2:H$964,$J11)</f>
-        <v>1</v>
-      </c>
-      <c r="O11" s="4">
-        <f>SUM(K11:N11)</f>
-        <v>2</v>
+      <c r="O11" s="3">
+        <f t="shared" si="3"/>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="15.75" customHeight="1"/>
@@ -968,500 +1053,500 @@
     <row r="41" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="42" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="43" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A43" s="6"/>
-      <c r="B43" s="6"/>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
     </row>
     <row r="44" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
     </row>
     <row r="45" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A45" s="6"/>
-      <c r="B45" s="6"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
     </row>
     <row r="46" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A46" s="6"/>
-      <c r="B46" s="6"/>
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
     </row>
     <row r="47" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A47" s="6"/>
-      <c r="B47" s="6"/>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
     </row>
     <row r="48" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A48" s="6"/>
-      <c r="B48" s="6"/>
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
     </row>
     <row r="49" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A49" s="6"/>
-      <c r="B49" s="6"/>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
     </row>
     <row r="50" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A50" s="6"/>
-      <c r="B50" s="6"/>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
     </row>
     <row r="51" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A51" s="6"/>
-      <c r="B51" s="6"/>
+      <c r="A51" s="4"/>
+      <c r="B51" s="4"/>
     </row>
     <row r="52" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A52" s="6"/>
-      <c r="B52" s="6"/>
+      <c r="A52" s="4"/>
+      <c r="B52" s="4"/>
     </row>
     <row r="53" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A53" s="6"/>
-      <c r="B53" s="6"/>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
     </row>
     <row r="54" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A54" s="6"/>
-      <c r="B54" s="6"/>
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
     </row>
     <row r="55" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A55" s="6"/>
-      <c r="B55" s="6"/>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
     </row>
     <row r="56" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A56" s="6"/>
-      <c r="B56" s="6"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
     </row>
     <row r="57" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A57" s="6"/>
-      <c r="B57" s="6"/>
+      <c r="A57" s="4"/>
+      <c r="B57" s="4"/>
     </row>
     <row r="58" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A58" s="6"/>
-      <c r="B58" s="6"/>
+      <c r="A58" s="4"/>
+      <c r="B58" s="4"/>
     </row>
     <row r="59" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
+      <c r="A59" s="4"/>
+      <c r="B59" s="4"/>
     </row>
     <row r="60" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A60" s="6"/>
-      <c r="B60" s="6"/>
+      <c r="A60" s="4"/>
+      <c r="B60" s="4"/>
     </row>
     <row r="61" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A61" s="6"/>
-      <c r="B61" s="6"/>
+      <c r="A61" s="4"/>
+      <c r="B61" s="4"/>
     </row>
     <row r="62" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A62" s="6"/>
-      <c r="B62" s="6"/>
+      <c r="A62" s="4"/>
+      <c r="B62" s="4"/>
     </row>
     <row r="63" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A63" s="6"/>
-      <c r="B63" s="6"/>
+      <c r="A63" s="4"/>
+      <c r="B63" s="4"/>
     </row>
     <row r="64" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A64" s="6"/>
-      <c r="B64" s="6"/>
+      <c r="A64" s="4"/>
+      <c r="B64" s="4"/>
     </row>
     <row r="65" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A65" s="6"/>
-      <c r="B65" s="6"/>
+      <c r="A65" s="4"/>
+      <c r="B65" s="4"/>
     </row>
     <row r="66" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A66" s="6"/>
-      <c r="B66" s="6"/>
+      <c r="A66" s="4"/>
+      <c r="B66" s="4"/>
     </row>
     <row r="67" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A67" s="6"/>
-      <c r="B67" s="6"/>
+      <c r="A67" s="4"/>
+      <c r="B67" s="4"/>
     </row>
     <row r="68" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A68" s="6"/>
-      <c r="B68" s="6"/>
+      <c r="A68" s="4"/>
+      <c r="B68" s="4"/>
     </row>
     <row r="69" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A69" s="6"/>
-      <c r="B69" s="6"/>
+      <c r="A69" s="4"/>
+      <c r="B69" s="4"/>
     </row>
     <row r="70" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A70" s="6"/>
-      <c r="B70" s="6"/>
+      <c r="A70" s="4"/>
+      <c r="B70" s="4"/>
     </row>
     <row r="71" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A71" s="6"/>
-      <c r="B71" s="6"/>
+      <c r="A71" s="4"/>
+      <c r="B71" s="4"/>
     </row>
     <row r="72" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A72" s="6"/>
-      <c r="B72" s="6"/>
+      <c r="A72" s="4"/>
+      <c r="B72" s="4"/>
     </row>
     <row r="73" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A73" s="6"/>
-      <c r="B73" s="6"/>
+      <c r="A73" s="4"/>
+      <c r="B73" s="4"/>
     </row>
     <row r="74" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A74" s="6"/>
-      <c r="B74" s="6"/>
+      <c r="A74" s="4"/>
+      <c r="B74" s="4"/>
     </row>
     <row r="75" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A75" s="6"/>
-      <c r="B75" s="6"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
     </row>
     <row r="76" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A76" s="6"/>
-      <c r="B76" s="6"/>
+      <c r="A76" s="4"/>
+      <c r="B76" s="4"/>
     </row>
     <row r="77" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A77" s="6"/>
-      <c r="B77" s="6"/>
+      <c r="A77" s="4"/>
+      <c r="B77" s="4"/>
     </row>
     <row r="78" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A78" s="6"/>
-      <c r="B78" s="6"/>
+      <c r="A78" s="4"/>
+      <c r="B78" s="4"/>
     </row>
     <row r="79" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A79" s="6"/>
-      <c r="B79" s="6"/>
+      <c r="A79" s="4"/>
+      <c r="B79" s="4"/>
     </row>
     <row r="80" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A80" s="6"/>
-      <c r="B80" s="6"/>
+      <c r="A80" s="4"/>
+      <c r="B80" s="4"/>
     </row>
     <row r="81" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A81" s="6"/>
-      <c r="B81" s="6"/>
+      <c r="A81" s="4"/>
+      <c r="B81" s="4"/>
     </row>
     <row r="82" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="6"/>
+      <c r="A82" s="4"/>
+      <c r="B82" s="4"/>
     </row>
     <row r="83" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A83" s="6"/>
-      <c r="B83" s="6"/>
+      <c r="A83" s="4"/>
+      <c r="B83" s="4"/>
     </row>
     <row r="84" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A84" s="6"/>
-      <c r="B84" s="6"/>
+      <c r="A84" s="4"/>
+      <c r="B84" s="4"/>
     </row>
     <row r="85" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A85" s="6"/>
-      <c r="B85" s="6"/>
+      <c r="A85" s="4"/>
+      <c r="B85" s="4"/>
     </row>
     <row r="86" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A86" s="6"/>
-      <c r="B86" s="6"/>
+      <c r="A86" s="4"/>
+      <c r="B86" s="4"/>
     </row>
     <row r="87" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A87" s="6"/>
-      <c r="B87" s="6"/>
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
     </row>
     <row r="88" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A88" s="6"/>
-      <c r="B88" s="6"/>
+      <c r="A88" s="4"/>
+      <c r="B88" s="4"/>
     </row>
     <row r="89" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A89" s="6"/>
-      <c r="B89" s="6"/>
+      <c r="A89" s="4"/>
+      <c r="B89" s="4"/>
     </row>
     <row r="90" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A90" s="6"/>
-      <c r="B90" s="6"/>
+      <c r="A90" s="4"/>
+      <c r="B90" s="4"/>
     </row>
     <row r="91" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A91" s="6"/>
-      <c r="B91" s="6"/>
+      <c r="A91" s="4"/>
+      <c r="B91" s="4"/>
     </row>
     <row r="92" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A92" s="6"/>
-      <c r="B92" s="6"/>
+      <c r="A92" s="4"/>
+      <c r="B92" s="4"/>
     </row>
     <row r="93" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A93" s="6"/>
-      <c r="B93" s="6"/>
+      <c r="A93" s="4"/>
+      <c r="B93" s="4"/>
     </row>
     <row r="94" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A94" s="6"/>
-      <c r="B94" s="6"/>
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
     </row>
     <row r="95" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A95" s="6"/>
-      <c r="B95" s="6"/>
+      <c r="A95" s="4"/>
+      <c r="B95" s="4"/>
     </row>
     <row r="96" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A96" s="6"/>
-      <c r="B96" s="6"/>
+      <c r="A96" s="4"/>
+      <c r="B96" s="4"/>
     </row>
     <row r="97" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A97" s="6"/>
-      <c r="B97" s="6"/>
+      <c r="A97" s="4"/>
+      <c r="B97" s="4"/>
     </row>
     <row r="98" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A98" s="6"/>
-      <c r="B98" s="6"/>
+      <c r="A98" s="4"/>
+      <c r="B98" s="4"/>
     </row>
     <row r="99" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A99" s="6"/>
-      <c r="B99" s="6"/>
+      <c r="A99" s="4"/>
+      <c r="B99" s="4"/>
     </row>
     <row r="100" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A100" s="6"/>
-      <c r="B100" s="6"/>
+      <c r="A100" s="4"/>
+      <c r="B100" s="4"/>
     </row>
     <row r="101" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A101" s="6"/>
-      <c r="B101" s="6"/>
+      <c r="A101" s="4"/>
+      <c r="B101" s="4"/>
     </row>
     <row r="102" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A102" s="6"/>
-      <c r="B102" s="6"/>
+      <c r="A102" s="4"/>
+      <c r="B102" s="4"/>
     </row>
     <row r="103" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A103" s="6"/>
-      <c r="B103" s="6"/>
+      <c r="A103" s="4"/>
+      <c r="B103" s="4"/>
     </row>
     <row r="104" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A104" s="6"/>
-      <c r="B104" s="6"/>
+      <c r="A104" s="4"/>
+      <c r="B104" s="4"/>
     </row>
     <row r="105" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A105" s="6"/>
-      <c r="B105" s="6"/>
+      <c r="A105" s="4"/>
+      <c r="B105" s="4"/>
     </row>
     <row r="106" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A106" s="6"/>
-      <c r="B106" s="6"/>
+      <c r="A106" s="4"/>
+      <c r="B106" s="4"/>
     </row>
     <row r="107" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A107" s="6"/>
-      <c r="B107" s="6"/>
+      <c r="A107" s="4"/>
+      <c r="B107" s="4"/>
     </row>
     <row r="108" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A108" s="6"/>
-      <c r="B108" s="6"/>
+      <c r="A108" s="4"/>
+      <c r="B108" s="4"/>
     </row>
     <row r="109" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A109" s="6"/>
-      <c r="B109" s="6"/>
+      <c r="A109" s="4"/>
+      <c r="B109" s="4"/>
     </row>
     <row r="110" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A110" s="6"/>
-      <c r="B110" s="6"/>
+      <c r="A110" s="4"/>
+      <c r="B110" s="4"/>
     </row>
     <row r="111" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A111" s="6"/>
-      <c r="B111" s="6"/>
+      <c r="A111" s="4"/>
+      <c r="B111" s="4"/>
     </row>
     <row r="112" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A112" s="6"/>
-      <c r="B112" s="6"/>
+      <c r="A112" s="4"/>
+      <c r="B112" s="4"/>
     </row>
     <row r="113" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A113" s="6"/>
-      <c r="B113" s="6"/>
+      <c r="A113" s="4"/>
+      <c r="B113" s="4"/>
     </row>
     <row r="114" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A114" s="6"/>
-      <c r="B114" s="6"/>
+      <c r="A114" s="4"/>
+      <c r="B114" s="4"/>
     </row>
     <row r="115" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A115" s="6"/>
-      <c r="B115" s="6"/>
+      <c r="A115" s="4"/>
+      <c r="B115" s="4"/>
     </row>
     <row r="116" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6"/>
+      <c r="A116" s="4"/>
+      <c r="B116" s="4"/>
     </row>
     <row r="117" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A117" s="6"/>
-      <c r="B117" s="6"/>
+      <c r="A117" s="4"/>
+      <c r="B117" s="4"/>
     </row>
     <row r="118" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A118" s="6"/>
-      <c r="B118" s="6"/>
+      <c r="A118" s="4"/>
+      <c r="B118" s="4"/>
     </row>
     <row r="119" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A119" s="6"/>
-      <c r="B119" s="6"/>
+      <c r="A119" s="4"/>
+      <c r="B119" s="4"/>
     </row>
     <row r="120" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6"/>
+      <c r="A120" s="4"/>
+      <c r="B120" s="4"/>
     </row>
     <row r="121" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A121" s="6"/>
-      <c r="B121" s="6"/>
+      <c r="A121" s="4"/>
+      <c r="B121" s="4"/>
     </row>
     <row r="122" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A122" s="6"/>
-      <c r="B122" s="6"/>
+      <c r="A122" s="4"/>
+      <c r="B122" s="4"/>
     </row>
     <row r="123" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A123" s="6"/>
-      <c r="B123" s="6"/>
+      <c r="A123" s="4"/>
+      <c r="B123" s="4"/>
     </row>
     <row r="124" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A124" s="6"/>
-      <c r="B124" s="6"/>
+      <c r="A124" s="4"/>
+      <c r="B124" s="4"/>
     </row>
     <row r="125" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A125" s="6"/>
-      <c r="B125" s="6"/>
+      <c r="A125" s="4"/>
+      <c r="B125" s="4"/>
     </row>
     <row r="126" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A126" s="6"/>
-      <c r="B126" s="6"/>
+      <c r="A126" s="4"/>
+      <c r="B126" s="4"/>
     </row>
     <row r="127" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A127" s="6"/>
-      <c r="B127" s="6"/>
+      <c r="A127" s="4"/>
+      <c r="B127" s="4"/>
     </row>
     <row r="128" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A128" s="6"/>
-      <c r="B128" s="6"/>
+      <c r="A128" s="4"/>
+      <c r="B128" s="4"/>
     </row>
     <row r="129" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A129" s="6"/>
-      <c r="B129" s="6"/>
+      <c r="A129" s="4"/>
+      <c r="B129" s="4"/>
     </row>
     <row r="130" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A130" s="6"/>
-      <c r="B130" s="6"/>
+      <c r="A130" s="4"/>
+      <c r="B130" s="4"/>
     </row>
     <row r="131" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A131" s="6"/>
-      <c r="B131" s="6"/>
+      <c r="A131" s="4"/>
+      <c r="B131" s="4"/>
     </row>
     <row r="132" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A132" s="6"/>
-      <c r="B132" s="6"/>
+      <c r="A132" s="4"/>
+      <c r="B132" s="4"/>
     </row>
     <row r="133" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A133" s="6"/>
-      <c r="B133" s="6"/>
+      <c r="A133" s="4"/>
+      <c r="B133" s="4"/>
     </row>
     <row r="134" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A134" s="6"/>
-      <c r="B134" s="6"/>
+      <c r="A134" s="4"/>
+      <c r="B134" s="4"/>
     </row>
     <row r="135" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A135" s="6"/>
-      <c r="B135" s="6"/>
+      <c r="A135" s="4"/>
+      <c r="B135" s="4"/>
     </row>
     <row r="136" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A136" s="6"/>
-      <c r="B136" s="6"/>
+      <c r="A136" s="4"/>
+      <c r="B136" s="4"/>
     </row>
     <row r="137" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A137" s="6"/>
-      <c r="B137" s="6"/>
+      <c r="A137" s="4"/>
+      <c r="B137" s="4"/>
     </row>
     <row r="138" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A138" s="6"/>
-      <c r="B138" s="6"/>
+      <c r="A138" s="4"/>
+      <c r="B138" s="4"/>
     </row>
     <row r="139" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A139" s="6"/>
-      <c r="B139" s="6"/>
+      <c r="A139" s="4"/>
+      <c r="B139" s="4"/>
     </row>
     <row r="140" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A140" s="6"/>
-      <c r="B140" s="6"/>
+      <c r="A140" s="4"/>
+      <c r="B140" s="4"/>
     </row>
     <row r="141" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A141" s="6"/>
-      <c r="B141" s="6"/>
+      <c r="A141" s="4"/>
+      <c r="B141" s="4"/>
     </row>
     <row r="142" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A142" s="6"/>
-      <c r="B142" s="6"/>
+      <c r="A142" s="4"/>
+      <c r="B142" s="4"/>
     </row>
     <row r="143" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
+      <c r="A143" s="4"/>
+      <c r="B143" s="4"/>
     </row>
     <row r="144" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A144" s="6"/>
-      <c r="B144" s="6"/>
+      <c r="A144" s="4"/>
+      <c r="B144" s="4"/>
     </row>
     <row r="145" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A145" s="6"/>
-      <c r="B145" s="6"/>
+      <c r="A145" s="4"/>
+      <c r="B145" s="4"/>
     </row>
     <row r="146" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A146" s="6"/>
-      <c r="B146" s="6"/>
+      <c r="A146" s="4"/>
+      <c r="B146" s="4"/>
     </row>
     <row r="147" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A147" s="6"/>
-      <c r="B147" s="6"/>
+      <c r="A147" s="4"/>
+      <c r="B147" s="4"/>
     </row>
     <row r="148" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A148" s="6"/>
-      <c r="B148" s="6"/>
+      <c r="A148" s="4"/>
+      <c r="B148" s="4"/>
     </row>
     <row r="149" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A149" s="6"/>
-      <c r="B149" s="6"/>
+      <c r="A149" s="4"/>
+      <c r="B149" s="4"/>
     </row>
     <row r="150" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A150" s="6"/>
-      <c r="B150" s="6"/>
+      <c r="A150" s="4"/>
+      <c r="B150" s="4"/>
     </row>
     <row r="151" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A151" s="6"/>
-      <c r="B151" s="6"/>
+      <c r="A151" s="4"/>
+      <c r="B151" s="4"/>
     </row>
     <row r="152" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A152" s="6"/>
-      <c r="B152" s="6"/>
+      <c r="A152" s="4"/>
+      <c r="B152" s="4"/>
     </row>
     <row r="153" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A153" s="6"/>
-      <c r="B153" s="6"/>
+      <c r="A153" s="4"/>
+      <c r="B153" s="4"/>
     </row>
     <row r="154" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A154" s="6"/>
-      <c r="B154" s="6"/>
+      <c r="A154" s="4"/>
+      <c r="B154" s="4"/>
     </row>
     <row r="155" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A155" s="6"/>
-      <c r="B155" s="6"/>
+      <c r="A155" s="4"/>
+      <c r="B155" s="4"/>
     </row>
     <row r="156" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A156" s="6"/>
-      <c r="B156" s="6"/>
+      <c r="A156" s="4"/>
+      <c r="B156" s="4"/>
     </row>
     <row r="157" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A157" s="6"/>
-      <c r="B157" s="6"/>
+      <c r="A157" s="4"/>
+      <c r="B157" s="4"/>
     </row>
     <row r="158" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A158" s="6"/>
-      <c r="B158" s="6"/>
+      <c r="A158" s="4"/>
+      <c r="B158" s="4"/>
     </row>
     <row r="159" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A159" s="6"/>
-      <c r="B159" s="6"/>
+      <c r="A159" s="4"/>
+      <c r="B159" s="4"/>
     </row>
     <row r="160" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A160" s="6"/>
-      <c r="B160" s="6"/>
+      <c r="A160" s="4"/>
+      <c r="B160" s="4"/>
     </row>
     <row r="161" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A161" s="6"/>
-      <c r="B161" s="6"/>
+      <c r="A161" s="4"/>
+      <c r="B161" s="4"/>
     </row>
     <row r="162" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A162" s="6"/>
-      <c r="B162" s="6"/>
+      <c r="A162" s="4"/>
+      <c r="B162" s="4"/>
     </row>
     <row r="163" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A163" s="6"/>
-      <c r="B163" s="6"/>
+      <c r="A163" s="4"/>
+      <c r="B163" s="4"/>
     </row>
     <row r="164" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A164" s="6"/>
-      <c r="B164" s="6"/>
+      <c r="A164" s="4"/>
+      <c r="B164" s="4"/>
     </row>
     <row r="165" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A165" s="6"/>
-      <c r="B165" s="6"/>
+      <c r="A165" s="4"/>
+      <c r="B165" s="4"/>
     </row>
     <row r="166" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A166" s="6"/>
-      <c r="B166" s="6"/>
+      <c r="A166" s="4"/>
+      <c r="B166" s="4"/>
     </row>
     <row r="167" spans="1:2" ht="15.75" customHeight="1"/>
     <row r="168" spans="1:2" ht="15.75" customHeight="1"/>
@@ -2243,16 +2328,6 @@
     <row r="944" ht="15.75" customHeight="1"/>
   </sheetData>
   <autoFilter ref="J1:O12" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="E2:G2 E4:G6 F7:G7 E8:G8 E43:G944 F3:G3">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$C2="away"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H8 H43:H944">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$C2="home"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/JO12-1/JO12-1_Volunteers.xlsx
+++ b/JO12-1/JO12-1_Volunteers.xlsx
@@ -171,7 +171,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -191,6 +191,9 @@
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf quotePrefix="1" borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -560,8 +563,8 @@
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="5">
-        <v>3.0</v>
+      <c r="A4" s="11">
+        <v>2.0</v>
       </c>
       <c r="B4" s="6">
         <v>46256.0</v>
@@ -609,8 +612,8 @@
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="5">
-        <v>4.0</v>
+      <c r="A5" s="11">
+        <v>3.0</v>
       </c>
       <c r="B5" s="6">
         <v>46263.0</v>
@@ -621,13 +624,13 @@
       <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="11" t="s">
+      <c r="E5" s="12" t="s">
         <v>15</v>
       </c>
       <c r="F5" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="11" t="s">
+      <c r="G5" s="12" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="9" t="s">
@@ -658,8 +661,8 @@
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="5">
-        <v>5.0</v>
+      <c r="A6" s="11">
+        <v>4.0</v>
       </c>
       <c r="B6" s="6">
         <v>46270.0</v>
@@ -679,7 +682,7 @@
       <c r="G6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="13" t="s">
         <v>21</v>
       </c>
       <c r="J6" s="4" t="s">
@@ -707,8 +710,8 @@
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="5">
-        <v>6.0</v>
+      <c r="A7" s="11">
+        <v>5.0</v>
       </c>
       <c r="B7" s="6">
         <v>46277.0</v>
@@ -756,8 +759,8 @@
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="5">
-        <v>7.0</v>
+      <c r="A8" s="11">
+        <v>6.0</v>
       </c>
       <c r="B8" s="6">
         <v>46284.0</v>
@@ -777,7 +780,7 @@
       <c r="G8" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="13" t="s">
         <v>14</v>
       </c>
       <c r="J8" s="4" t="s">
@@ -805,8 +808,8 @@
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="5">
-        <v>8.0</v>
+      <c r="A9" s="11">
+        <v>7.0</v>
       </c>
       <c r="B9" s="6">
         <v>46291.0</v>
@@ -817,10 +820,10 @@
       <c r="D9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="11" t="s">
+      <c r="E9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="12" t="s">
         <v>15</v>
       </c>
       <c r="G9" s="8" t="s">
@@ -854,8 +857,8 @@
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="5">
-        <v>9.0</v>
+      <c r="A10" s="11">
+        <v>8.0</v>
       </c>
       <c r="B10" s="6">
         <v>46298.0</v>
@@ -959,500 +962,500 @@
     <row r="41" ht="15.75" customHeight="1"/>
     <row r="42" ht="15.75" customHeight="1"/>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="13"/>
-      <c r="B45" s="13"/>
+      <c r="A45" s="14"/>
+      <c r="B45" s="14"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="13"/>
-      <c r="B46" s="13"/>
+      <c r="A46" s="14"/>
+      <c r="B46" s="14"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="13"/>
-      <c r="B47" s="13"/>
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="13"/>
-      <c r="B48" s="13"/>
+      <c r="A48" s="14"/>
+      <c r="B48" s="14"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="13"/>
-      <c r="B49" s="13"/>
+      <c r="A49" s="14"/>
+      <c r="B49" s="14"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="13"/>
-      <c r="B50" s="13"/>
+      <c r="A50" s="14"/>
+      <c r="B50" s="14"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
+      <c r="A51" s="14"/>
+      <c r="B51" s="14"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
+      <c r="A52" s="14"/>
+      <c r="B52" s="14"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="13"/>
-      <c r="B53" s="13"/>
+      <c r="A53" s="14"/>
+      <c r="B53" s="14"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="13"/>
-      <c r="B54" s="13"/>
+      <c r="A54" s="14"/>
+      <c r="B54" s="14"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="13"/>
-      <c r="B55" s="13"/>
+      <c r="A55" s="14"/>
+      <c r="B55" s="14"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
+      <c r="A56" s="14"/>
+      <c r="B56" s="14"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="13"/>
-      <c r="B57" s="13"/>
+      <c r="A57" s="14"/>
+      <c r="B57" s="14"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="13"/>
-      <c r="B58" s="13"/>
+      <c r="A58" s="14"/>
+      <c r="B58" s="14"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="13"/>
-      <c r="B59" s="13"/>
+      <c r="A59" s="14"/>
+      <c r="B59" s="14"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="13"/>
-      <c r="B60" s="13"/>
+      <c r="A60" s="14"/>
+      <c r="B60" s="14"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="13"/>
-      <c r="B61" s="13"/>
+      <c r="A61" s="14"/>
+      <c r="B61" s="14"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="13"/>
-      <c r="B62" s="13"/>
+      <c r="A62" s="14"/>
+      <c r="B62" s="14"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="13"/>
-      <c r="B63" s="13"/>
+      <c r="A63" s="14"/>
+      <c r="B63" s="14"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="13"/>
-      <c r="B64" s="13"/>
+      <c r="A64" s="14"/>
+      <c r="B64" s="14"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="13"/>
-      <c r="B65" s="13"/>
+      <c r="A65" s="14"/>
+      <c r="B65" s="14"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="13"/>
-      <c r="B66" s="13"/>
+      <c r="A66" s="14"/>
+      <c r="B66" s="14"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="13"/>
-      <c r="B67" s="13"/>
+      <c r="A67" s="14"/>
+      <c r="B67" s="14"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="13"/>
-      <c r="B68" s="13"/>
+      <c r="A68" s="14"/>
+      <c r="B68" s="14"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="13"/>
-      <c r="B69" s="13"/>
+      <c r="A69" s="14"/>
+      <c r="B69" s="14"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="13"/>
-      <c r="B70" s="13"/>
+      <c r="A70" s="14"/>
+      <c r="B70" s="14"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="13"/>
-      <c r="B71" s="13"/>
+      <c r="A71" s="14"/>
+      <c r="B71" s="14"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="13"/>
-      <c r="B72" s="13"/>
+      <c r="A72" s="14"/>
+      <c r="B72" s="14"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="13"/>
-      <c r="B73" s="13"/>
+      <c r="A73" s="14"/>
+      <c r="B73" s="14"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="13"/>
-      <c r="B74" s="13"/>
+      <c r="A74" s="14"/>
+      <c r="B74" s="14"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="13"/>
-      <c r="B75" s="13"/>
+      <c r="A75" s="14"/>
+      <c r="B75" s="14"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="13"/>
-      <c r="B76" s="13"/>
+      <c r="A76" s="14"/>
+      <c r="B76" s="14"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="13"/>
-      <c r="B77" s="13"/>
+      <c r="A77" s="14"/>
+      <c r="B77" s="14"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="13"/>
-      <c r="B78" s="13"/>
+      <c r="A78" s="14"/>
+      <c r="B78" s="14"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="13"/>
-      <c r="B79" s="13"/>
+      <c r="A79" s="14"/>
+      <c r="B79" s="14"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="13"/>
-      <c r="B80" s="13"/>
+      <c r="A80" s="14"/>
+      <c r="B80" s="14"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="13"/>
-      <c r="B81" s="13"/>
+      <c r="A81" s="14"/>
+      <c r="B81" s="14"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="13"/>
-      <c r="B82" s="13"/>
+      <c r="A82" s="14"/>
+      <c r="B82" s="14"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="13"/>
-      <c r="B83" s="13"/>
+      <c r="A83" s="14"/>
+      <c r="B83" s="14"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="13"/>
-      <c r="B84" s="13"/>
+      <c r="A84" s="14"/>
+      <c r="B84" s="14"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="13"/>
-      <c r="B85" s="13"/>
+      <c r="A85" s="14"/>
+      <c r="B85" s="14"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="13"/>
-      <c r="B86" s="13"/>
+      <c r="A86" s="14"/>
+      <c r="B86" s="14"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="13"/>
-      <c r="B87" s="13"/>
+      <c r="A87" s="14"/>
+      <c r="B87" s="14"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="13"/>
-      <c r="B88" s="13"/>
+      <c r="A88" s="14"/>
+      <c r="B88" s="14"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="13"/>
-      <c r="B89" s="13"/>
+      <c r="A89" s="14"/>
+      <c r="B89" s="14"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="13"/>
-      <c r="B90" s="13"/>
+      <c r="A90" s="14"/>
+      <c r="B90" s="14"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="13"/>
-      <c r="B91" s="13"/>
+      <c r="A91" s="14"/>
+      <c r="B91" s="14"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="13"/>
-      <c r="B92" s="13"/>
+      <c r="A92" s="14"/>
+      <c r="B92" s="14"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="13"/>
-      <c r="B93" s="13"/>
+      <c r="A93" s="14"/>
+      <c r="B93" s="14"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="13"/>
-      <c r="B94" s="13"/>
+      <c r="A94" s="14"/>
+      <c r="B94" s="14"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="13"/>
-      <c r="B95" s="13"/>
+      <c r="A95" s="14"/>
+      <c r="B95" s="14"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="13"/>
-      <c r="B96" s="13"/>
+      <c r="A96" s="14"/>
+      <c r="B96" s="14"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="13"/>
-      <c r="B97" s="13"/>
+      <c r="A97" s="14"/>
+      <c r="B97" s="14"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="13"/>
-      <c r="B98" s="13"/>
+      <c r="A98" s="14"/>
+      <c r="B98" s="14"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="13"/>
-      <c r="B99" s="13"/>
+      <c r="A99" s="14"/>
+      <c r="B99" s="14"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="13"/>
-      <c r="B100" s="13"/>
+      <c r="A100" s="14"/>
+      <c r="B100" s="14"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="13"/>
-      <c r="B101" s="13"/>
+      <c r="A101" s="14"/>
+      <c r="B101" s="14"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="13"/>
-      <c r="B102" s="13"/>
+      <c r="A102" s="14"/>
+      <c r="B102" s="14"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="13"/>
-      <c r="B103" s="13"/>
+      <c r="A103" s="14"/>
+      <c r="B103" s="14"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="13"/>
-      <c r="B104" s="13"/>
+      <c r="A104" s="14"/>
+      <c r="B104" s="14"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="13"/>
-      <c r="B105" s="13"/>
+      <c r="A105" s="14"/>
+      <c r="B105" s="14"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="13"/>
-      <c r="B106" s="13"/>
+      <c r="A106" s="14"/>
+      <c r="B106" s="14"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="13"/>
-      <c r="B107" s="13"/>
+      <c r="A107" s="14"/>
+      <c r="B107" s="14"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="13"/>
-      <c r="B108" s="13"/>
+      <c r="A108" s="14"/>
+      <c r="B108" s="14"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="13"/>
-      <c r="B109" s="13"/>
+      <c r="A109" s="14"/>
+      <c r="B109" s="14"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="13"/>
-      <c r="B110" s="13"/>
+      <c r="A110" s="14"/>
+      <c r="B110" s="14"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="13"/>
-      <c r="B111" s="13"/>
+      <c r="A111" s="14"/>
+      <c r="B111" s="14"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="13"/>
-      <c r="B112" s="13"/>
+      <c r="A112" s="14"/>
+      <c r="B112" s="14"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="13"/>
-      <c r="B113" s="13"/>
+      <c r="A113" s="14"/>
+      <c r="B113" s="14"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="13"/>
-      <c r="B114" s="13"/>
+      <c r="A114" s="14"/>
+      <c r="B114" s="14"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="13"/>
-      <c r="B115" s="13"/>
+      <c r="A115" s="14"/>
+      <c r="B115" s="14"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="13"/>
-      <c r="B116" s="13"/>
+      <c r="A116" s="14"/>
+      <c r="B116" s="14"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="13"/>
-      <c r="B117" s="13"/>
+      <c r="A117" s="14"/>
+      <c r="B117" s="14"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="13"/>
-      <c r="B118" s="13"/>
+      <c r="A118" s="14"/>
+      <c r="B118" s="14"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="13"/>
-      <c r="B119" s="13"/>
+      <c r="A119" s="14"/>
+      <c r="B119" s="14"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="13"/>
-      <c r="B120" s="13"/>
+      <c r="A120" s="14"/>
+      <c r="B120" s="14"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="13"/>
-      <c r="B121" s="13"/>
+      <c r="A121" s="14"/>
+      <c r="B121" s="14"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="13"/>
-      <c r="B122" s="13"/>
+      <c r="A122" s="14"/>
+      <c r="B122" s="14"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="13"/>
-      <c r="B123" s="13"/>
+      <c r="A123" s="14"/>
+      <c r="B123" s="14"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="13"/>
-      <c r="B124" s="13"/>
+      <c r="A124" s="14"/>
+      <c r="B124" s="14"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="13"/>
-      <c r="B125" s="13"/>
+      <c r="A125" s="14"/>
+      <c r="B125" s="14"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="13"/>
-      <c r="B126" s="13"/>
+      <c r="A126" s="14"/>
+      <c r="B126" s="14"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="13"/>
-      <c r="B127" s="13"/>
+      <c r="A127" s="14"/>
+      <c r="B127" s="14"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="13"/>
-      <c r="B128" s="13"/>
+      <c r="A128" s="14"/>
+      <c r="B128" s="14"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="13"/>
-      <c r="B129" s="13"/>
+      <c r="A129" s="14"/>
+      <c r="B129" s="14"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="13"/>
-      <c r="B130" s="13"/>
+      <c r="A130" s="14"/>
+      <c r="B130" s="14"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="13"/>
-      <c r="B131" s="13"/>
+      <c r="A131" s="14"/>
+      <c r="B131" s="14"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="13"/>
-      <c r="B132" s="13"/>
+      <c r="A132" s="14"/>
+      <c r="B132" s="14"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="13"/>
-      <c r="B133" s="13"/>
+      <c r="A133" s="14"/>
+      <c r="B133" s="14"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="13"/>
-      <c r="B134" s="13"/>
+      <c r="A134" s="14"/>
+      <c r="B134" s="14"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="13"/>
-      <c r="B135" s="13"/>
+      <c r="A135" s="14"/>
+      <c r="B135" s="14"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="13"/>
-      <c r="B136" s="13"/>
+      <c r="A136" s="14"/>
+      <c r="B136" s="14"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="13"/>
-      <c r="B137" s="13"/>
+      <c r="A137" s="14"/>
+      <c r="B137" s="14"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="13"/>
-      <c r="B138" s="13"/>
+      <c r="A138" s="14"/>
+      <c r="B138" s="14"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="13"/>
-      <c r="B139" s="13"/>
+      <c r="A139" s="14"/>
+      <c r="B139" s="14"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="13"/>
-      <c r="B140" s="13"/>
+      <c r="A140" s="14"/>
+      <c r="B140" s="14"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="13"/>
-      <c r="B141" s="13"/>
+      <c r="A141" s="14"/>
+      <c r="B141" s="14"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="13"/>
-      <c r="B142" s="13"/>
+      <c r="A142" s="14"/>
+      <c r="B142" s="14"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="13"/>
-      <c r="B143" s="13"/>
+      <c r="A143" s="14"/>
+      <c r="B143" s="14"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="13"/>
-      <c r="B144" s="13"/>
+      <c r="A144" s="14"/>
+      <c r="B144" s="14"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="13"/>
-      <c r="B145" s="13"/>
+      <c r="A145" s="14"/>
+      <c r="B145" s="14"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="13"/>
-      <c r="B146" s="13"/>
+      <c r="A146" s="14"/>
+      <c r="B146" s="14"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="13"/>
-      <c r="B147" s="13"/>
+      <c r="A147" s="14"/>
+      <c r="B147" s="14"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="13"/>
-      <c r="B148" s="13"/>
+      <c r="A148" s="14"/>
+      <c r="B148" s="14"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="13"/>
-      <c r="B149" s="13"/>
+      <c r="A149" s="14"/>
+      <c r="B149" s="14"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="13"/>
-      <c r="B150" s="13"/>
+      <c r="A150" s="14"/>
+      <c r="B150" s="14"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="13"/>
-      <c r="B151" s="13"/>
+      <c r="A151" s="14"/>
+      <c r="B151" s="14"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="13"/>
-      <c r="B152" s="13"/>
+      <c r="A152" s="14"/>
+      <c r="B152" s="14"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="13"/>
-      <c r="B153" s="13"/>
+      <c r="A153" s="14"/>
+      <c r="B153" s="14"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="13"/>
-      <c r="B154" s="13"/>
+      <c r="A154" s="14"/>
+      <c r="B154" s="14"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="13"/>
-      <c r="B155" s="13"/>
+      <c r="A155" s="14"/>
+      <c r="B155" s="14"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="13"/>
-      <c r="B156" s="13"/>
+      <c r="A156" s="14"/>
+      <c r="B156" s="14"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="13"/>
-      <c r="B157" s="13"/>
+      <c r="A157" s="14"/>
+      <c r="B157" s="14"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="13"/>
-      <c r="B158" s="13"/>
+      <c r="A158" s="14"/>
+      <c r="B158" s="14"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="13"/>
-      <c r="B159" s="13"/>
+      <c r="A159" s="14"/>
+      <c r="B159" s="14"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="13"/>
-      <c r="B160" s="13"/>
+      <c r="A160" s="14"/>
+      <c r="B160" s="14"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="13"/>
-      <c r="B161" s="13"/>
+      <c r="A161" s="14"/>
+      <c r="B161" s="14"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="13"/>
-      <c r="B162" s="13"/>
+      <c r="A162" s="14"/>
+      <c r="B162" s="14"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="13"/>
-      <c r="B163" s="13"/>
+      <c r="A163" s="14"/>
+      <c r="B163" s="14"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="13"/>
-      <c r="B164" s="13"/>
+      <c r="A164" s="14"/>
+      <c r="B164" s="14"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="13"/>
-      <c r="B165" s="13"/>
+      <c r="A165" s="14"/>
+      <c r="B165" s="14"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="13"/>
-      <c r="B166" s="13"/>
+      <c r="A166" s="14"/>
+      <c r="B166" s="14"/>
     </row>
     <row r="167" ht="15.75" customHeight="1"/>
     <row r="168" ht="15.75" customHeight="1"/>
